--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="209">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:07 AM</t>
+    <t>6/16/2026, 5:20:48 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>0.00s</t>
+    <t>9.16s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,6 +103,9 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.47s</t>
+  </si>
+  <si>
     <t>TC-APP-02</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>App prevents submission on empty email or password fields</t>
   </si>
   <si>
+    <t>0.18s</t>
+  </si>
+  <si>
     <t>TC-APP-03</t>
   </si>
   <si>
@@ -121,6 +127,9 @@
     <t>Error label displays when email format is invalid</t>
   </si>
   <si>
+    <t>0.28s</t>
+  </si>
+  <si>
     <t>TC-APP-04</t>
   </si>
   <si>
@@ -130,6 +139,9 @@
     <t>App registers biometric device setup option in local state</t>
   </si>
   <si>
+    <t>0.15s</t>
+  </si>
+  <si>
     <t>TC-APP-05</t>
   </si>
   <si>
@@ -139,6 +151,9 @@
     <t>Dashboard balance, income, and expense summary widgets render</t>
   </si>
   <si>
+    <t>0.25s</t>
+  </si>
+  <si>
     <t>TC-APP-06</t>
   </si>
   <si>
@@ -148,6 +163,9 @@
     <t>Balance summary card resolves within view limits</t>
   </si>
   <si>
+    <t>0.36s</t>
+  </si>
+  <si>
     <t>TC-APP-07</t>
   </si>
   <si>
@@ -157,6 +175,9 @@
     <t>Pull to refresh updates transaction listings from background storage</t>
   </si>
   <si>
+    <t>0.20s</t>
+  </si>
+  <si>
     <t>TC-APP-08</t>
   </si>
   <si>
@@ -166,6 +187,9 @@
     <t>Income sheet modal slides into view</t>
   </si>
   <si>
+    <t>0.29s</t>
+  </si>
+  <si>
     <t>TC-APP-09</t>
   </si>
   <si>
@@ -175,6 +199,9 @@
     <t>Category select holds Salary, Freelance, and Investments options</t>
   </si>
   <si>
+    <t>0.40s</t>
+  </si>
+  <si>
     <t>TC-APP-10</t>
   </si>
   <si>
@@ -184,6 +211,9 @@
     <t>Income fields accept numeric and descriptive inputs</t>
   </si>
   <si>
+    <t>0.32s</t>
+  </si>
+  <si>
     <t>TC-APP-11</t>
   </si>
   <si>
@@ -193,6 +223,9 @@
     <t>Missing amount triggers mobile error highlights</t>
   </si>
   <si>
+    <t>0.21s</t>
+  </si>
+  <si>
     <t>TC-APP-12</t>
   </si>
   <si>
@@ -202,6 +235,9 @@
     <t>Expense sheet slides up with focus on Category dropdown</t>
   </si>
   <si>
+    <t>0.42s</t>
+  </si>
+  <si>
     <t>TC-APP-13</t>
   </si>
   <si>
@@ -211,6 +247,9 @@
     <t>Expense logging works and decreases overall dashboard balance</t>
   </si>
   <si>
+    <t>0.26s</t>
+  </si>
+  <si>
     <t>TC-APP-14</t>
   </si>
   <si>
@@ -220,6 +259,9 @@
     <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
   </si>
   <si>
+    <t>0.33s</t>
+  </si>
+  <si>
     <t>TC-APP-15</t>
   </si>
   <si>
@@ -238,6 +280,9 @@
     <t>Active budget progress limiters are visible</t>
   </si>
   <si>
+    <t>0.23s</t>
+  </si>
+  <si>
     <t>TC-APP-17</t>
   </si>
   <si>
@@ -247,6 +292,9 @@
     <t>Progress bar limits adjust to new budget configurations</t>
   </si>
   <si>
+    <t>0.39s</t>
+  </si>
+  <si>
     <t>TC-APP-18</t>
   </si>
   <si>
@@ -256,6 +304,9 @@
     <t>Alert popup loads when transaction breaches designated cap threshold</t>
   </si>
   <si>
+    <t>0.38s</t>
+  </si>
+  <si>
     <t>TC-APP-19</t>
   </si>
   <si>
@@ -283,6 +334,9 @@
     <t>Successful transactions prompt immediate mobile success toast alert</t>
   </si>
   <si>
+    <t>0.43s</t>
+  </si>
+  <si>
     <t>TC-APP-22</t>
   </si>
   <si>
@@ -301,6 +355,9 @@
     <t>Profile screen loads fields for user settings adjustments</t>
   </si>
   <si>
+    <t>0.22s</t>
+  </si>
+  <si>
     <t>TC-APP-24</t>
   </si>
   <si>
@@ -355,6 +412,9 @@
     <t>Double tap exits execution thread and backgrounds app</t>
   </si>
   <si>
+    <t>0.45s</t>
+  </si>
+  <si>
     <t>TC-APP-30</t>
   </si>
   <si>
@@ -364,6 +424,9 @@
     <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
   </si>
   <si>
+    <t>0.35s</t>
+  </si>
+  <si>
     <t>Failure Message</t>
   </si>
   <si>
@@ -391,7 +454,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:00 AM</t>
+    <t>6/16/2026, 5:20:47 AM</t>
   </si>
   <si>
     <t>LoginPage</t>
@@ -1166,21 +1229,21 @@
         <v>28</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>27</v>
@@ -1189,21 +1252,21 @@
         <v>28</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>27</v>
@@ -1212,21 +1275,21 @@
         <v>28</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>27</v>
@@ -1235,21 +1298,21 @@
         <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>27</v>
@@ -1258,21 +1321,21 @@
         <v>28</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1281,21 +1344,21 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1304,21 +1367,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1327,21 +1390,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1350,21 +1413,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1373,21 +1436,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1396,21 +1459,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1419,21 +1482,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1442,21 +1505,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1465,21 +1528,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1488,21 +1551,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1511,21 +1574,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1534,21 +1597,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1557,21 +1620,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1580,21 +1643,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1603,21 +1666,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1626,21 +1689,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1649,21 +1712,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1672,21 +1735,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1695,21 +1758,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1718,21 +1781,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1741,21 +1804,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1764,21 +1827,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1787,21 +1850,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1810,21 +1873,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1833,7 +1896,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>15</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1865,27 +1928,27 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1908,75 +1971,75 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
@@ -1993,98 +2056,98 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
@@ -2095,81 +2158,81 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -2180,13 +2243,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
@@ -2197,64 +2260,64 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
@@ -2265,13 +2328,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
@@ -2282,30 +2345,30 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2316,30 +2379,30 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2350,13 +2413,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2367,115 +2430,115 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
@@ -2486,13 +2549,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
@@ -2503,30 +2566,30 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -2537,115 +2600,115 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
@@ -2656,13 +2719,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
@@ -2673,13 +2736,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
@@ -2690,30 +2753,30 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
@@ -2724,98 +2787,98 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
@@ -2826,183 +2889,183 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
@@ -3013,13 +3076,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
@@ -3030,13 +3093,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
@@ -3047,13 +3110,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3064,13 +3127,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
@@ -3081,30 +3144,30 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3115,98 +3178,98 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3217,81 +3280,81 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3302,13 +3365,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3319,13 +3382,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
@@ -3336,13 +3399,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
@@ -3353,13 +3416,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
@@ -3370,30 +3433,30 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="207">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 5:20:48 AM</t>
+    <t>6/16/2026, 5:29:22 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>9.16s</t>
+    <t>9.27s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.47s</t>
+    <t>0.46s</t>
   </si>
   <si>
     <t>TC-APP-02</t>
@@ -115,306 +115,306 @@
     <t>App prevents submission on empty email or password fields</t>
   </si>
   <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-APP-03</t>
+  </si>
+  <si>
+    <t>TC-APP-03: Validate login email address format checking rules</t>
+  </si>
+  <si>
+    <t>Error label displays when email format is invalid</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-APP-04</t>
+  </si>
+  <si>
+    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
+  </si>
+  <si>
+    <t>App registers biometric device setup option in local state</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-APP-05</t>
+  </si>
+  <si>
+    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
+  </si>
+  <si>
+    <t>Dashboard balance, income, and expense summary widgets render</t>
+  </si>
+  <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-APP-06</t>
+  </si>
+  <si>
+    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
+  </si>
+  <si>
+    <t>Balance summary card resolves within view limits</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-APP-07</t>
+  </si>
+  <si>
+    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
+  </si>
+  <si>
+    <t>Pull to refresh updates transaction listings from background storage</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-APP-08</t>
+  </si>
+  <si>
+    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
+  </si>
+  <si>
+    <t>Income sheet modal slides into view</t>
+  </si>
+  <si>
+    <t>TC-APP-09</t>
+  </si>
+  <si>
+    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
+  </si>
+  <si>
+    <t>Category select holds Salary, Freelance, and Investments options</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-APP-10</t>
+  </si>
+  <si>
+    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
+  </si>
+  <si>
+    <t>Income fields accept numeric and descriptive inputs</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-APP-11</t>
+  </si>
+  <si>
+    <t>TC-APP-11: Validate empty income form submission error indicators</t>
+  </si>
+  <si>
+    <t>Missing amount triggers mobile error highlights</t>
+  </si>
+  <si>
+    <t>TC-APP-12</t>
+  </si>
+  <si>
+    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
+  </si>
+  <si>
+    <t>Expense sheet slides up with focus on Category dropdown</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-APP-13</t>
+  </si>
+  <si>
+    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
+  </si>
+  <si>
+    <t>Expense logging works and decreases overall dashboard balance</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-APP-14</t>
+  </si>
+  <si>
+    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
+  </si>
+  <si>
+    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
+  </si>
+  <si>
+    <t>TC-APP-15</t>
+  </si>
+  <si>
+    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
+  </si>
+  <si>
+    <t>Soft keyboard changes to numeric layout on amount field focus</t>
+  </si>
+  <si>
+    <t>TC-APP-16</t>
+  </si>
+  <si>
+    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
+  </si>
+  <si>
+    <t>Active budget progress limiters are visible</t>
+  </si>
+  <si>
+    <t>TC-APP-17</t>
+  </si>
+  <si>
+    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
+  </si>
+  <si>
+    <t>Progress bar limits adjust to new budget configurations</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-APP-18</t>
+  </si>
+  <si>
+    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
+  </si>
+  <si>
+    <t>Alert popup loads when transaction breaches designated cap threshold</t>
+  </si>
+  <si>
     <t>0.18s</t>
   </si>
   <si>
-    <t>TC-APP-03</t>
-  </si>
-  <si>
-    <t>TC-APP-03: Validate login email address format checking rules</t>
-  </si>
-  <si>
-    <t>Error label displays when email format is invalid</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-APP-04</t>
-  </si>
-  <si>
-    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
-  </si>
-  <si>
-    <t>App registers biometric device setup option in local state</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-APP-05</t>
-  </si>
-  <si>
-    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
-  </si>
-  <si>
-    <t>Dashboard balance, income, and expense summary widgets render</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-APP-06</t>
-  </si>
-  <si>
-    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
-  </si>
-  <si>
-    <t>Balance summary card resolves within view limits</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-APP-07</t>
-  </si>
-  <si>
-    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
-  </si>
-  <si>
-    <t>Pull to refresh updates transaction listings from background storage</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-APP-08</t>
-  </si>
-  <si>
-    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
-  </si>
-  <si>
-    <t>Income sheet modal slides into view</t>
+    <t>TC-APP-19</t>
+  </si>
+  <si>
+    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
+  </si>
+  <si>
+    <t>Distribution chart switches between absolute values and percentages</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-APP-20</t>
+  </si>
+  <si>
+    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
+  </si>
+  <si>
+    <t>Push alert fires sending current limits allocations reminders</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-APP-21</t>
+  </si>
+  <si>
+    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
+  </si>
+  <si>
+    <t>Successful transactions prompt immediate mobile success toast alert</t>
   </si>
   <si>
     <t>0.29s</t>
   </si>
   <si>
-    <t>TC-APP-09</t>
-  </si>
-  <si>
-    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
-  </si>
-  <si>
-    <t>Category select holds Salary, Freelance, and Investments options</t>
+    <t>TC-APP-22</t>
+  </si>
+  <si>
+    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
+  </si>
+  <si>
+    <t>Swiping a notification alert row removes it from notifications panel</t>
+  </si>
+  <si>
+    <t>TC-APP-23</t>
+  </si>
+  <si>
+    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
+  </si>
+  <si>
+    <t>Profile screen loads fields for user settings adjustments</t>
+  </si>
+  <si>
+    <t>TC-APP-24</t>
+  </si>
+  <si>
+    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
+  </si>
+  <si>
+    <t>Display Name changes update the user info values on Save</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-APP-25</t>
+  </si>
+  <si>
+    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
+  </si>
+  <si>
+    <t>Preferred currency symbol alters default currency label layout</t>
+  </si>
+  <si>
+    <t>TC-APP-26</t>
+  </si>
+  <si>
+    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
+  </si>
+  <si>
+    <t>Dialog queries permissions access to camera device for receipts scan</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-APP-27</t>
+  </si>
+  <si>
+    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
+  </si>
+  <si>
+    <t>Toggling dark theme alters app styling variables colors</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-APP-28</t>
+  </si>
+  <si>
+    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
+  </si>
+  <si>
+    <t>Logout prompts verification warning dialog</t>
+  </si>
+  <si>
+    <t>TC-APP-29</t>
+  </si>
+  <si>
+    <t>TC-APP-29: Verify double tap mobile back button exits the application safely</t>
+  </si>
+  <si>
+    <t>Double tap exits execution thread and backgrounds app</t>
   </si>
   <si>
     <t>0.40s</t>
   </si>
   <si>
-    <t>TC-APP-10</t>
-  </si>
-  <si>
-    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
-  </si>
-  <si>
-    <t>Income fields accept numeric and descriptive inputs</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-APP-11</t>
-  </si>
-  <si>
-    <t>TC-APP-11: Validate empty income form submission error indicators</t>
-  </si>
-  <si>
-    <t>Missing amount triggers mobile error highlights</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-APP-12</t>
-  </si>
-  <si>
-    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
-  </si>
-  <si>
-    <t>Expense sheet slides up with focus on Category dropdown</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-APP-13</t>
-  </si>
-  <si>
-    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
-  </si>
-  <si>
-    <t>Expense logging works and decreases overall dashboard balance</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-APP-14</t>
-  </si>
-  <si>
-    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
-  </si>
-  <si>
-    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-APP-15</t>
-  </si>
-  <si>
-    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
-  </si>
-  <si>
-    <t>Soft keyboard changes to numeric layout on amount field focus</t>
-  </si>
-  <si>
-    <t>TC-APP-16</t>
-  </si>
-  <si>
-    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
-  </si>
-  <si>
-    <t>Active budget progress limiters are visible</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-APP-17</t>
-  </si>
-  <si>
-    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
-  </si>
-  <si>
-    <t>Progress bar limits adjust to new budget configurations</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-APP-18</t>
-  </si>
-  <si>
-    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
-  </si>
-  <si>
-    <t>Alert popup loads when transaction breaches designated cap threshold</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-APP-19</t>
-  </si>
-  <si>
-    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
-  </si>
-  <si>
-    <t>Distribution chart switches between absolute values and percentages</t>
-  </si>
-  <si>
-    <t>TC-APP-20</t>
-  </si>
-  <si>
-    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
-  </si>
-  <si>
-    <t>Push alert fires sending current limits allocations reminders</t>
-  </si>
-  <si>
-    <t>TC-APP-21</t>
-  </si>
-  <si>
-    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
-  </si>
-  <si>
-    <t>Successful transactions prompt immediate mobile success toast alert</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-APP-22</t>
-  </si>
-  <si>
-    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
-  </si>
-  <si>
-    <t>Swiping a notification alert row removes it from notifications panel</t>
-  </si>
-  <si>
-    <t>TC-APP-23</t>
-  </si>
-  <si>
-    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
-  </si>
-  <si>
-    <t>Profile screen loads fields for user settings adjustments</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-APP-24</t>
-  </si>
-  <si>
-    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
-  </si>
-  <si>
-    <t>Display Name changes update the user info values on Save</t>
-  </si>
-  <si>
-    <t>TC-APP-25</t>
-  </si>
-  <si>
-    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
-  </si>
-  <si>
-    <t>Preferred currency symbol alters default currency label layout</t>
-  </si>
-  <si>
-    <t>TC-APP-26</t>
-  </si>
-  <si>
-    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
-  </si>
-  <si>
-    <t>Dialog queries permissions access to camera device for receipts scan</t>
-  </si>
-  <si>
-    <t>TC-APP-27</t>
-  </si>
-  <si>
-    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
-  </si>
-  <si>
-    <t>Toggling dark theme alters app styling variables colors</t>
-  </si>
-  <si>
-    <t>TC-APP-28</t>
-  </si>
-  <si>
-    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
-  </si>
-  <si>
-    <t>Logout prompts verification warning dialog</t>
-  </si>
-  <si>
-    <t>TC-APP-29</t>
-  </si>
-  <si>
-    <t>TC-APP-29: Verify double tap mobile back button exits the application safely</t>
-  </si>
-  <si>
-    <t>Double tap exits execution thread and backgrounds app</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
     <t>TC-APP-30</t>
   </si>
   <si>
@@ -424,9 +424,6 @@
     <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
   </si>
   <si>
-    <t>0.35s</t>
-  </si>
-  <si>
     <t>Failure Message</t>
   </si>
   <si>
@@ -452,9 +449,6 @@
   </si>
   <si>
     <t>Remarks</t>
-  </si>
-  <si>
-    <t>6/16/2026, 5:20:47 AM</t>
   </si>
   <si>
     <t>LoginPage</t>
@@ -1390,21 +1384,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1413,21 +1407,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1436,21 +1430,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1459,21 +1453,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1482,21 +1476,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1505,21 +1499,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1528,21 +1522,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1556,16 +1550,16 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1574,21 +1568,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1597,21 +1591,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1620,21 +1614,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1643,21 +1637,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1666,21 +1660,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1689,21 +1683,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1712,21 +1706,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1735,21 +1729,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1758,21 +1752,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1781,21 +1775,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1804,21 +1798,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1827,7 +1821,7 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1850,7 +1844,7 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1896,7 +1890,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1928,27 +1922,27 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1971,75 +1965,75 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
@@ -2056,92 +2050,92 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
@@ -2158,75 +2152,75 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
@@ -2243,7 +2237,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
@@ -2260,58 +2254,58 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="D18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
@@ -2328,7 +2322,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
@@ -2345,24 +2339,24 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
@@ -2379,24 +2373,24 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
@@ -2413,13 +2407,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2430,115 +2424,115 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
@@ -2549,13 +2543,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
@@ -2566,30 +2560,30 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -2600,115 +2594,115 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
@@ -2719,13 +2713,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
@@ -2736,13 +2730,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
@@ -2753,30 +2747,30 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
@@ -2787,98 +2781,98 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
@@ -2889,183 +2883,183 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
@@ -3076,13 +3070,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
@@ -3093,13 +3087,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
@@ -3110,13 +3104,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3127,13 +3121,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
@@ -3144,30 +3138,30 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3178,98 +3172,98 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3280,81 +3274,81 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3365,13 +3359,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3382,13 +3376,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
@@ -3399,7 +3393,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>24</v>
@@ -3416,7 +3410,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>24</v>
@@ -3433,24 +3427,24 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>24</v>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 5:29:22 AM</t>
+    <t>6/16/2026, 5:37:50 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>9.27s</t>
+    <t>9.65s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,243 +103,249 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-APP-02</t>
+  </si>
+  <si>
+    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
+  </si>
+  <si>
+    <t>App prevents submission on empty email or password fields</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-APP-03</t>
+  </si>
+  <si>
+    <t>TC-APP-03: Validate login email address format checking rules</t>
+  </si>
+  <si>
+    <t>Error label displays when email format is invalid</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-APP-04</t>
+  </si>
+  <si>
+    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
+  </si>
+  <si>
+    <t>App registers biometric device setup option in local state</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-APP-05</t>
+  </si>
+  <si>
+    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
+  </si>
+  <si>
+    <t>Dashboard balance, income, and expense summary widgets render</t>
+  </si>
+  <si>
+    <t>TC-APP-06</t>
+  </si>
+  <si>
+    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
+  </si>
+  <si>
+    <t>Balance summary card resolves within view limits</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-APP-07</t>
+  </si>
+  <si>
+    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
+  </si>
+  <si>
+    <t>Pull to refresh updates transaction listings from background storage</t>
+  </si>
+  <si>
     <t>0.46s</t>
   </si>
   <si>
-    <t>TC-APP-02</t>
-  </si>
-  <si>
-    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
-  </si>
-  <si>
-    <t>App prevents submission on empty email or password fields</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-APP-03</t>
-  </si>
-  <si>
-    <t>TC-APP-03: Validate login email address format checking rules</t>
-  </si>
-  <si>
-    <t>Error label displays when email format is invalid</t>
+    <t>TC-APP-08</t>
+  </si>
+  <si>
+    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
+  </si>
+  <si>
+    <t>Income sheet modal slides into view</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-APP-09</t>
+  </si>
+  <si>
+    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
+  </si>
+  <si>
+    <t>Category select holds Salary, Freelance, and Investments options</t>
+  </si>
+  <si>
+    <t>0.48s</t>
+  </si>
+  <si>
+    <t>TC-APP-10</t>
+  </si>
+  <si>
+    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
+  </si>
+  <si>
+    <t>Income fields accept numeric and descriptive inputs</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-APP-11</t>
+  </si>
+  <si>
+    <t>TC-APP-11: Validate empty income form submission error indicators</t>
+  </si>
+  <si>
+    <t>Missing amount triggers mobile error highlights</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-APP-12</t>
+  </si>
+  <si>
+    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
+  </si>
+  <si>
+    <t>Expense sheet slides up with focus on Category dropdown</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-APP-13</t>
+  </si>
+  <si>
+    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
+  </si>
+  <si>
+    <t>Expense logging works and decreases overall dashboard balance</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-APP-14</t>
+  </si>
+  <si>
+    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
+  </si>
+  <si>
+    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
+  </si>
+  <si>
+    <t>TC-APP-15</t>
+  </si>
+  <si>
+    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
+  </si>
+  <si>
+    <t>Soft keyboard changes to numeric layout on amount field focus</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-APP-16</t>
+  </si>
+  <si>
+    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
+  </si>
+  <si>
+    <t>Active budget progress limiters are visible</t>
   </si>
   <si>
     <t>0.20s</t>
   </si>
   <si>
-    <t>TC-APP-04</t>
-  </si>
-  <si>
-    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
-  </si>
-  <si>
-    <t>App registers biometric device setup option in local state</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-APP-05</t>
-  </si>
-  <si>
-    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
-  </si>
-  <si>
-    <t>Dashboard balance, income, and expense summary widgets render</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-APP-06</t>
-  </si>
-  <si>
-    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
-  </si>
-  <si>
-    <t>Balance summary card resolves within view limits</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-APP-07</t>
-  </si>
-  <si>
-    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
-  </si>
-  <si>
-    <t>Pull to refresh updates transaction listings from background storage</t>
+    <t>TC-APP-17</t>
+  </si>
+  <si>
+    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
+  </si>
+  <si>
+    <t>Progress bar limits adjust to new budget configurations</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-APP-18</t>
+  </si>
+  <si>
+    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
+  </si>
+  <si>
+    <t>Alert popup loads when transaction breaches designated cap threshold</t>
   </si>
   <si>
     <t>0.26s</t>
   </si>
   <si>
-    <t>TC-APP-08</t>
-  </si>
-  <si>
-    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
-  </si>
-  <si>
-    <t>Income sheet modal slides into view</t>
-  </si>
-  <si>
-    <t>TC-APP-09</t>
-  </si>
-  <si>
-    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
-  </si>
-  <si>
-    <t>Category select holds Salary, Freelance, and Investments options</t>
+    <t>TC-APP-19</t>
+  </si>
+  <si>
+    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
+  </si>
+  <si>
+    <t>Distribution chart switches between absolute values and percentages</t>
+  </si>
+  <si>
+    <t>TC-APP-20</t>
+  </si>
+  <si>
+    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
+  </si>
+  <si>
+    <t>Push alert fires sending current limits allocations reminders</t>
   </si>
   <si>
     <t>0.19s</t>
   </si>
   <si>
-    <t>TC-APP-10</t>
-  </si>
-  <si>
-    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
-  </si>
-  <si>
-    <t>Income fields accept numeric and descriptive inputs</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-APP-11</t>
-  </si>
-  <si>
-    <t>TC-APP-11: Validate empty income form submission error indicators</t>
-  </si>
-  <si>
-    <t>Missing amount triggers mobile error highlights</t>
-  </si>
-  <si>
-    <t>TC-APP-12</t>
-  </si>
-  <si>
-    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
-  </si>
-  <si>
-    <t>Expense sheet slides up with focus on Category dropdown</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-APP-13</t>
-  </si>
-  <si>
-    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
-  </si>
-  <si>
-    <t>Expense logging works and decreases overall dashboard balance</t>
+    <t>TC-APP-21</t>
+  </si>
+  <si>
+    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
+  </si>
+  <si>
+    <t>Successful transactions prompt immediate mobile success toast alert</t>
+  </si>
+  <si>
+    <t>TC-APP-22</t>
+  </si>
+  <si>
+    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
+  </si>
+  <si>
+    <t>Swiping a notification alert row removes it from notifications panel</t>
   </si>
   <si>
     <t>0.25s</t>
   </si>
   <si>
-    <t>TC-APP-14</t>
-  </si>
-  <si>
-    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
-  </si>
-  <si>
-    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
-  </si>
-  <si>
-    <t>TC-APP-15</t>
-  </si>
-  <si>
-    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
-  </si>
-  <si>
-    <t>Soft keyboard changes to numeric layout on amount field focus</t>
-  </si>
-  <si>
-    <t>TC-APP-16</t>
-  </si>
-  <si>
-    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
-  </si>
-  <si>
-    <t>Active budget progress limiters are visible</t>
-  </si>
-  <si>
-    <t>TC-APP-17</t>
-  </si>
-  <si>
-    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
-  </si>
-  <si>
-    <t>Progress bar limits adjust to new budget configurations</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-APP-18</t>
-  </si>
-  <si>
-    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
-  </si>
-  <si>
-    <t>Alert popup loads when transaction breaches designated cap threshold</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
-    <t>TC-APP-19</t>
-  </si>
-  <si>
-    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
-  </si>
-  <si>
-    <t>Distribution chart switches between absolute values and percentages</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-APP-20</t>
-  </si>
-  <si>
-    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
-  </si>
-  <si>
-    <t>Push alert fires sending current limits allocations reminders</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-APP-21</t>
-  </si>
-  <si>
-    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
-  </si>
-  <si>
-    <t>Successful transactions prompt immediate mobile success toast alert</t>
-  </si>
-  <si>
-    <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-APP-22</t>
-  </si>
-  <si>
-    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
-  </si>
-  <si>
-    <t>Swiping a notification alert row removes it from notifications panel</t>
-  </si>
-  <si>
     <t>TC-APP-23</t>
   </si>
   <si>
@@ -349,6 +355,9 @@
     <t>Profile screen loads fields for user settings adjustments</t>
   </si>
   <si>
+    <t>0.30s</t>
+  </si>
+  <si>
     <t>TC-APP-24</t>
   </si>
   <si>
@@ -358,7 +367,7 @@
     <t>Display Name changes update the user info values on Save</t>
   </si>
   <si>
-    <t>0.35s</t>
+    <t>0.22s</t>
   </si>
   <si>
     <t>TC-APP-25</t>
@@ -379,9 +388,6 @@
     <t>Dialog queries permissions access to camera device for receipts scan</t>
   </si>
   <si>
-    <t>0.27s</t>
-  </si>
-  <si>
     <t>TC-APP-27</t>
   </si>
   <si>
@@ -391,9 +397,6 @@
     <t>Toggling dark theme alters app styling variables colors</t>
   </si>
   <si>
-    <t>0.41s</t>
-  </si>
-  <si>
     <t>TC-APP-28</t>
   </si>
   <si>
@@ -410,9 +413,6 @@
   </si>
   <si>
     <t>Double tap exits execution thread and backgrounds app</t>
-  </si>
-  <si>
-    <t>0.40s</t>
   </si>
   <si>
     <t>TC-APP-30</t>
@@ -1315,21 +1315,21 @@
         <v>28</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1338,21 +1338,21 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1361,21 +1361,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1384,7 +1384,7 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1453,21 +1453,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1476,21 +1476,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1499,21 +1499,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1522,21 +1522,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1545,21 +1545,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1568,21 +1568,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1591,21 +1591,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1614,21 +1614,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1637,21 +1637,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1660,21 +1660,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1683,21 +1683,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1706,21 +1706,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1729,21 +1729,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1752,21 +1752,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1775,21 +1775,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1798,21 +1798,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1821,21 +1821,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1844,21 +1844,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1867,7 +1867,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1890,7 +1890,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2328,7 +2328,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
@@ -2362,7 +2362,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2396,7 +2396,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -2702,7 +2702,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
@@ -2719,7 +2719,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
@@ -2736,7 +2736,7 @@
         <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
@@ -2770,7 +2770,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
@@ -2872,7 +2872,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
@@ -3059,7 +3059,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
@@ -3076,7 +3076,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
@@ -3093,7 +3093,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
@@ -3110,7 +3110,7 @@
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3127,7 +3127,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
@@ -3161,7 +3161,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3263,7 +3263,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3348,7 +3348,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3382,7 +3382,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
@@ -3399,7 +3399,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
@@ -3416,7 +3416,7 @@
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="209">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 5:37:50 AM</t>
+    <t>6/16/2026, 5:40:56 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>9.65s</t>
+    <t>8.82s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -115,7 +115,7 @@
     <t>App prevents submission on empty email or password fields</t>
   </si>
   <si>
-    <t>0.43s</t>
+    <t>0.26s</t>
   </si>
   <si>
     <t>TC-APP-03</t>
@@ -127,7 +127,7 @@
     <t>Error label displays when email format is invalid</t>
   </si>
   <si>
-    <t>0.37s</t>
+    <t>0.19s</t>
   </si>
   <si>
     <t>TC-APP-04</t>
@@ -139,280 +139,286 @@
     <t>App registers biometric device setup option in local state</t>
   </si>
   <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-APP-05</t>
+  </si>
+  <si>
+    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
+  </si>
+  <si>
+    <t>Dashboard balance, income, and expense summary widgets render</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-APP-06</t>
+  </si>
+  <si>
+    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
+  </si>
+  <si>
+    <t>Balance summary card resolves within view limits</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-APP-07</t>
+  </si>
+  <si>
+    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
+  </si>
+  <si>
+    <t>Pull to refresh updates transaction listings from background storage</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-APP-08</t>
+  </si>
+  <si>
+    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
+  </si>
+  <si>
+    <t>Income sheet modal slides into view</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-APP-09</t>
+  </si>
+  <si>
+    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
+  </si>
+  <si>
+    <t>Category select holds Salary, Freelance, and Investments options</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-APP-10</t>
+  </si>
+  <si>
+    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
+  </si>
+  <si>
+    <t>Income fields accept numeric and descriptive inputs</t>
+  </si>
+  <si>
     <t>0.40s</t>
   </si>
   <si>
-    <t>TC-APP-05</t>
-  </si>
-  <si>
-    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
-  </si>
-  <si>
-    <t>Dashboard balance, income, and expense summary widgets render</t>
-  </si>
-  <si>
-    <t>TC-APP-06</t>
-  </si>
-  <si>
-    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
-  </si>
-  <si>
-    <t>Balance summary card resolves within view limits</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-APP-07</t>
-  </si>
-  <si>
-    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
-  </si>
-  <si>
-    <t>Pull to refresh updates transaction listings from background storage</t>
+    <t>TC-APP-11</t>
+  </si>
+  <si>
+    <t>TC-APP-11: Validate empty income form submission error indicators</t>
+  </si>
+  <si>
+    <t>Missing amount triggers mobile error highlights</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-APP-12</t>
+  </si>
+  <si>
+    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
+  </si>
+  <si>
+    <t>Expense sheet slides up with focus on Category dropdown</t>
+  </si>
+  <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-APP-13</t>
+  </si>
+  <si>
+    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
+  </si>
+  <si>
+    <t>Expense logging works and decreases overall dashboard balance</t>
   </si>
   <si>
     <t>0.46s</t>
   </si>
   <si>
-    <t>TC-APP-08</t>
-  </si>
-  <si>
-    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
-  </si>
-  <si>
-    <t>Income sheet modal slides into view</t>
+    <t>TC-APP-14</t>
+  </si>
+  <si>
+    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
+  </si>
+  <si>
+    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-APP-15</t>
+  </si>
+  <si>
+    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
+  </si>
+  <si>
+    <t>Soft keyboard changes to numeric layout on amount field focus</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-APP-16</t>
+  </si>
+  <si>
+    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
+  </si>
+  <si>
+    <t>Active budget progress limiters are visible</t>
+  </si>
+  <si>
+    <t>TC-APP-17</t>
+  </si>
+  <si>
+    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
+  </si>
+  <si>
+    <t>Progress bar limits adjust to new budget configurations</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-APP-18</t>
+  </si>
+  <si>
+    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
+  </si>
+  <si>
+    <t>Alert popup loads when transaction breaches designated cap threshold</t>
+  </si>
+  <si>
+    <t>TC-APP-19</t>
+  </si>
+  <si>
+    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
+  </si>
+  <si>
+    <t>Distribution chart switches between absolute values and percentages</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-APP-20</t>
+  </si>
+  <si>
+    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
+  </si>
+  <si>
+    <t>Push alert fires sending current limits allocations reminders</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-APP-21</t>
+  </si>
+  <si>
+    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
+  </si>
+  <si>
+    <t>Successful transactions prompt immediate mobile success toast alert</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-APP-22</t>
+  </si>
+  <si>
+    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
+  </si>
+  <si>
+    <t>Swiping a notification alert row removes it from notifications panel</t>
+  </si>
+  <si>
+    <t>TC-APP-23</t>
+  </si>
+  <si>
+    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
+  </si>
+  <si>
+    <t>Profile screen loads fields for user settings adjustments</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-APP-24</t>
+  </si>
+  <si>
+    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
+  </si>
+  <si>
+    <t>Display Name changes update the user info values on Save</t>
   </si>
   <si>
     <t>0.17s</t>
   </si>
   <si>
-    <t>TC-APP-09</t>
-  </si>
-  <si>
-    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
-  </si>
-  <si>
-    <t>Category select holds Salary, Freelance, and Investments options</t>
-  </si>
-  <si>
-    <t>0.48s</t>
-  </si>
-  <si>
-    <t>TC-APP-10</t>
-  </si>
-  <si>
-    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
-  </si>
-  <si>
-    <t>Income fields accept numeric and descriptive inputs</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-APP-11</t>
-  </si>
-  <si>
-    <t>TC-APP-11: Validate empty income form submission error indicators</t>
-  </si>
-  <si>
-    <t>Missing amount triggers mobile error highlights</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
-    <t>TC-APP-12</t>
-  </si>
-  <si>
-    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
-  </si>
-  <si>
-    <t>Expense sheet slides up with focus on Category dropdown</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-APP-13</t>
-  </si>
-  <si>
-    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
-  </si>
-  <si>
-    <t>Expense logging works and decreases overall dashboard balance</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-APP-14</t>
-  </si>
-  <si>
-    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
-  </si>
-  <si>
-    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
-  </si>
-  <si>
-    <t>TC-APP-15</t>
-  </si>
-  <si>
-    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
-  </si>
-  <si>
-    <t>Soft keyboard changes to numeric layout on amount field focus</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-APP-16</t>
-  </si>
-  <si>
-    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
-  </si>
-  <si>
-    <t>Active budget progress limiters are visible</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-APP-17</t>
-  </si>
-  <si>
-    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
-  </si>
-  <si>
-    <t>Progress bar limits adjust to new budget configurations</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-APP-18</t>
-  </si>
-  <si>
-    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
-  </si>
-  <si>
-    <t>Alert popup loads when transaction breaches designated cap threshold</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-APP-19</t>
-  </si>
-  <si>
-    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
-  </si>
-  <si>
-    <t>Distribution chart switches between absolute values and percentages</t>
-  </si>
-  <si>
-    <t>TC-APP-20</t>
-  </si>
-  <si>
-    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
-  </si>
-  <si>
-    <t>Push alert fires sending current limits allocations reminders</t>
-  </si>
-  <si>
-    <t>0.19s</t>
-  </si>
-  <si>
-    <t>TC-APP-21</t>
-  </si>
-  <si>
-    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
-  </si>
-  <si>
-    <t>Successful transactions prompt immediate mobile success toast alert</t>
-  </si>
-  <si>
-    <t>TC-APP-22</t>
-  </si>
-  <si>
-    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
-  </si>
-  <si>
-    <t>Swiping a notification alert row removes it from notifications panel</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-APP-23</t>
-  </si>
-  <si>
-    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
-  </si>
-  <si>
-    <t>Profile screen loads fields for user settings adjustments</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-APP-24</t>
-  </si>
-  <si>
-    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
-  </si>
-  <si>
-    <t>Display Name changes update the user info values on Save</t>
+    <t>TC-APP-25</t>
+  </si>
+  <si>
+    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
+  </si>
+  <si>
+    <t>Preferred currency symbol alters default currency label layout</t>
+  </si>
+  <si>
+    <t>TC-APP-26</t>
+  </si>
+  <si>
+    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
+  </si>
+  <si>
+    <t>Dialog queries permissions access to camera device for receipts scan</t>
+  </si>
+  <si>
+    <t>TC-APP-27</t>
+  </si>
+  <si>
+    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
+  </si>
+  <si>
+    <t>Toggling dark theme alters app styling variables colors</t>
+  </si>
+  <si>
+    <t>TC-APP-28</t>
+  </si>
+  <si>
+    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
+  </si>
+  <si>
+    <t>Logout prompts verification warning dialog</t>
+  </si>
+  <si>
+    <t>TC-APP-29</t>
+  </si>
+  <si>
+    <t>TC-APP-29: Verify double tap mobile back button exits the application safely</t>
+  </si>
+  <si>
+    <t>Double tap exits execution thread and backgrounds app</t>
   </si>
   <si>
     <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-APP-25</t>
-  </si>
-  <si>
-    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
-  </si>
-  <si>
-    <t>Preferred currency symbol alters default currency label layout</t>
-  </si>
-  <si>
-    <t>TC-APP-26</t>
-  </si>
-  <si>
-    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
-  </si>
-  <si>
-    <t>Dialog queries permissions access to camera device for receipts scan</t>
-  </si>
-  <si>
-    <t>TC-APP-27</t>
-  </si>
-  <si>
-    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
-  </si>
-  <si>
-    <t>Toggling dark theme alters app styling variables colors</t>
-  </si>
-  <si>
-    <t>TC-APP-28</t>
-  </si>
-  <si>
-    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
-  </si>
-  <si>
-    <t>Logout prompts verification warning dialog</t>
-  </si>
-  <si>
-    <t>TC-APP-29</t>
-  </si>
-  <si>
-    <t>TC-APP-29: Verify double tap mobile back button exits the application safely</t>
-  </si>
-  <si>
-    <t>Double tap exits execution thread and backgrounds app</t>
   </si>
   <si>
     <t>TC-APP-30</t>
@@ -1315,21 +1321,21 @@
         <v>28</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1338,21 +1344,21 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1361,21 +1367,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1384,21 +1390,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1407,21 +1413,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1430,21 +1436,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1453,21 +1459,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1476,21 +1482,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1499,21 +1505,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1522,21 +1528,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1545,21 +1551,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1568,21 +1574,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1591,21 +1597,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1614,7 +1620,7 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1637,21 +1643,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1660,21 +1666,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1683,21 +1689,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1706,21 +1712,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1729,21 +1735,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1752,21 +1758,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1775,21 +1781,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1798,21 +1804,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1821,21 +1827,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1844,21 +1850,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1867,21 +1873,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1890,7 +1896,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1922,27 +1928,27 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1965,19 +1971,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1985,16 +1991,16 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2002,16 +2008,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2019,16 +2025,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2053,16 +2059,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2070,16 +2076,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2087,16 +2093,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2104,16 +2110,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2121,16 +2127,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2155,16 +2161,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2172,16 +2178,16 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2189,16 +2195,16 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2206,16 +2212,16 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2257,16 +2263,16 @@
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2274,16 +2280,16 @@
         <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2291,16 +2297,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2328,7 +2334,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
@@ -2342,16 +2348,16 @@
         <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2362,7 +2368,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2376,16 +2382,16 @@
         <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2396,7 +2402,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2413,7 +2419,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2427,16 +2433,16 @@
         <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2444,16 +2450,16 @@
         <v>3</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2461,16 +2467,16 @@
         <v>3</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2478,16 +2484,16 @@
         <v>3</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2495,16 +2501,16 @@
         <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2512,16 +2518,16 @@
         <v>3</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2532,7 +2538,7 @@
         <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
@@ -2549,7 +2555,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
@@ -2563,16 +2569,16 @@
         <v>3</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2583,7 +2589,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -2597,16 +2603,16 @@
         <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2614,16 +2620,16 @@
         <v>3</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2631,16 +2637,16 @@
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2648,16 +2654,16 @@
         <v>3</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2665,16 +2671,16 @@
         <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2682,16 +2688,16 @@
         <v>3</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2702,7 +2708,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
@@ -2719,7 +2725,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
@@ -2736,7 +2742,7 @@
         <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
@@ -2750,16 +2756,16 @@
         <v>3</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2770,7 +2776,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
@@ -2784,16 +2790,16 @@
         <v>3</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2801,16 +2807,16 @@
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2818,16 +2824,16 @@
         <v>3</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2835,16 +2841,16 @@
         <v>3</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2852,16 +2858,16 @@
         <v>3</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2872,7 +2878,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
@@ -2886,16 +2892,16 @@
         <v>3</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2903,16 +2909,16 @@
         <v>3</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2920,16 +2926,16 @@
         <v>3</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2937,16 +2943,16 @@
         <v>3</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2954,16 +2960,16 @@
         <v>3</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2971,16 +2977,16 @@
         <v>3</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2988,16 +2994,16 @@
         <v>3</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3005,16 +3011,16 @@
         <v>3</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3022,16 +3028,16 @@
         <v>3</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3039,16 +3045,16 @@
         <v>3</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3059,7 +3065,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
@@ -3093,7 +3099,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
@@ -3110,7 +3116,7 @@
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3127,7 +3133,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
@@ -3141,16 +3147,16 @@
         <v>3</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3161,7 +3167,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3175,16 +3181,16 @@
         <v>3</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3192,16 +3198,16 @@
         <v>3</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3209,16 +3215,16 @@
         <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3226,16 +3232,16 @@
         <v>3</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3243,16 +3249,16 @@
         <v>3</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3263,7 +3269,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3277,16 +3283,16 @@
         <v>3</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3294,16 +3300,16 @@
         <v>3</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3311,16 +3317,16 @@
         <v>3</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3328,16 +3334,16 @@
         <v>3</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3348,7 +3354,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3365,7 +3371,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3382,7 +3388,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
@@ -3399,7 +3405,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
@@ -3416,7 +3422,7 @@
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
@@ -3430,16 +3436,16 @@
         <v>3</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3450,7 +3456,7 @@
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="206">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 5:40:56 AM</t>
+    <t>6/16/2026, 5:48:31 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.82s</t>
+    <t>8.86s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,331 +103,322 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-APP-02</t>
+  </si>
+  <si>
+    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
+  </si>
+  <si>
+    <t>App prevents submission on empty email or password fields</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-APP-03</t>
+  </si>
+  <si>
+    <t>TC-APP-03: Validate login email address format checking rules</t>
+  </si>
+  <si>
+    <t>Error label displays when email format is invalid</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-APP-04</t>
+  </si>
+  <si>
+    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
+  </si>
+  <si>
+    <t>App registers biometric device setup option in local state</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-APP-05</t>
+  </si>
+  <si>
+    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
+  </si>
+  <si>
+    <t>Dashboard balance, income, and expense summary widgets render</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-APP-06</t>
+  </si>
+  <si>
+    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
+  </si>
+  <si>
+    <t>Balance summary card resolves within view limits</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-APP-07</t>
+  </si>
+  <si>
+    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
+  </si>
+  <si>
+    <t>Pull to refresh updates transaction listings from background storage</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-APP-08</t>
+  </si>
+  <si>
+    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
+  </si>
+  <si>
+    <t>Income sheet modal slides into view</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-APP-09</t>
+  </si>
+  <si>
+    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
+  </si>
+  <si>
+    <t>Category select holds Salary, Freelance, and Investments options</t>
+  </si>
+  <si>
     <t>0.47s</t>
   </si>
   <si>
-    <t>TC-APP-02</t>
-  </si>
-  <si>
-    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
-  </si>
-  <si>
-    <t>App prevents submission on empty email or password fields</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-APP-03</t>
-  </si>
-  <si>
-    <t>TC-APP-03: Validate login email address format checking rules</t>
-  </si>
-  <si>
-    <t>Error label displays when email format is invalid</t>
+    <t>TC-APP-10</t>
+  </si>
+  <si>
+    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
+  </si>
+  <si>
+    <t>Income fields accept numeric and descriptive inputs</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-APP-11</t>
+  </si>
+  <si>
+    <t>TC-APP-11: Validate empty income form submission error indicators</t>
+  </si>
+  <si>
+    <t>Missing amount triggers mobile error highlights</t>
+  </si>
+  <si>
+    <t>TC-APP-12</t>
+  </si>
+  <si>
+    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
+  </si>
+  <si>
+    <t>Expense sheet slides up with focus on Category dropdown</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-APP-13</t>
+  </si>
+  <si>
+    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
+  </si>
+  <si>
+    <t>Expense logging works and decreases overall dashboard balance</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-APP-14</t>
+  </si>
+  <si>
+    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
+  </si>
+  <si>
+    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
+  </si>
+  <si>
+    <t>TC-APP-15</t>
+  </si>
+  <si>
+    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
+  </si>
+  <si>
+    <t>Soft keyboard changes to numeric layout on amount field focus</t>
+  </si>
+  <si>
+    <t>TC-APP-16</t>
+  </si>
+  <si>
+    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
+  </si>
+  <si>
+    <t>Active budget progress limiters are visible</t>
+  </si>
+  <si>
+    <t>TC-APP-17</t>
+  </si>
+  <si>
+    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
+  </si>
+  <si>
+    <t>Progress bar limits adjust to new budget configurations</t>
+  </si>
+  <si>
+    <t>TC-APP-18</t>
+  </si>
+  <si>
+    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
+  </si>
+  <si>
+    <t>Alert popup loads when transaction breaches designated cap threshold</t>
+  </si>
+  <si>
+    <t>TC-APP-19</t>
+  </si>
+  <si>
+    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
+  </si>
+  <si>
+    <t>Distribution chart switches between absolute values and percentages</t>
+  </si>
+  <si>
+    <t>TC-APP-20</t>
+  </si>
+  <si>
+    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
+  </si>
+  <si>
+    <t>Push alert fires sending current limits allocations reminders</t>
+  </si>
+  <si>
+    <t>TC-APP-21</t>
+  </si>
+  <si>
+    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
+  </si>
+  <si>
+    <t>Successful transactions prompt immediate mobile success toast alert</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-APP-22</t>
+  </si>
+  <si>
+    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
+  </si>
+  <si>
+    <t>Swiping a notification alert row removes it from notifications panel</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-APP-23</t>
+  </si>
+  <si>
+    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
+  </si>
+  <si>
+    <t>Profile screen loads fields for user settings adjustments</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-APP-24</t>
+  </si>
+  <si>
+    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
+  </si>
+  <si>
+    <t>Display Name changes update the user info values on Save</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-APP-25</t>
+  </si>
+  <si>
+    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
+  </si>
+  <si>
+    <t>Preferred currency symbol alters default currency label layout</t>
   </si>
   <si>
     <t>0.19s</t>
   </si>
   <si>
-    <t>TC-APP-04</t>
-  </si>
-  <si>
-    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
-  </si>
-  <si>
-    <t>App registers biometric device setup option in local state</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-APP-05</t>
-  </si>
-  <si>
-    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
-  </si>
-  <si>
-    <t>Dashboard balance, income, and expense summary widgets render</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-APP-06</t>
-  </si>
-  <si>
-    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
-  </si>
-  <si>
-    <t>Balance summary card resolves within view limits</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-APP-07</t>
-  </si>
-  <si>
-    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
-  </si>
-  <si>
-    <t>Pull to refresh updates transaction listings from background storage</t>
+    <t>TC-APP-26</t>
+  </si>
+  <si>
+    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
+  </si>
+  <si>
+    <t>Dialog queries permissions access to camera device for receipts scan</t>
+  </si>
+  <si>
+    <t>TC-APP-27</t>
+  </si>
+  <si>
+    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
+  </si>
+  <si>
+    <t>Toggling dark theme alters app styling variables colors</t>
+  </si>
+  <si>
+    <t>TC-APP-28</t>
+  </si>
+  <si>
+    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
+  </si>
+  <si>
+    <t>Logout prompts verification warning dialog</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-APP-29</t>
+  </si>
+  <si>
+    <t>TC-APP-29: Verify double tap mobile back button exits the application safely</t>
+  </si>
+  <si>
+    <t>Double tap exits execution thread and backgrounds app</t>
+  </si>
+  <si>
+    <t>TC-APP-30</t>
+  </si>
+  <si>
+    <t>TC-APP-30: Verify complete authentication details and cached tokens wipe on Logout</t>
+  </si>
+  <si>
+    <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
   </si>
   <si>
     <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-APP-08</t>
-  </si>
-  <si>
-    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
-  </si>
-  <si>
-    <t>Income sheet modal slides into view</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-APP-09</t>
-  </si>
-  <si>
-    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
-  </si>
-  <si>
-    <t>Category select holds Salary, Freelance, and Investments options</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-APP-10</t>
-  </si>
-  <si>
-    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
-  </si>
-  <si>
-    <t>Income fields accept numeric and descriptive inputs</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-APP-11</t>
-  </si>
-  <si>
-    <t>TC-APP-11: Validate empty income form submission error indicators</t>
-  </si>
-  <si>
-    <t>Missing amount triggers mobile error highlights</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-APP-12</t>
-  </si>
-  <si>
-    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
-  </si>
-  <si>
-    <t>Expense sheet slides up with focus on Category dropdown</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-APP-13</t>
-  </si>
-  <si>
-    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
-  </si>
-  <si>
-    <t>Expense logging works and decreases overall dashboard balance</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-APP-14</t>
-  </si>
-  <si>
-    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
-  </si>
-  <si>
-    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-APP-15</t>
-  </si>
-  <si>
-    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
-  </si>
-  <si>
-    <t>Soft keyboard changes to numeric layout on amount field focus</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-APP-16</t>
-  </si>
-  <si>
-    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
-  </si>
-  <si>
-    <t>Active budget progress limiters are visible</t>
-  </si>
-  <si>
-    <t>TC-APP-17</t>
-  </si>
-  <si>
-    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
-  </si>
-  <si>
-    <t>Progress bar limits adjust to new budget configurations</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-APP-18</t>
-  </si>
-  <si>
-    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
-  </si>
-  <si>
-    <t>Alert popup loads when transaction breaches designated cap threshold</t>
-  </si>
-  <si>
-    <t>TC-APP-19</t>
-  </si>
-  <si>
-    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
-  </si>
-  <si>
-    <t>Distribution chart switches between absolute values and percentages</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-APP-20</t>
-  </si>
-  <si>
-    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
-  </si>
-  <si>
-    <t>Push alert fires sending current limits allocations reminders</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-APP-21</t>
-  </si>
-  <si>
-    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
-  </si>
-  <si>
-    <t>Successful transactions prompt immediate mobile success toast alert</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-APP-22</t>
-  </si>
-  <si>
-    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
-  </si>
-  <si>
-    <t>Swiping a notification alert row removes it from notifications panel</t>
-  </si>
-  <si>
-    <t>TC-APP-23</t>
-  </si>
-  <si>
-    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
-  </si>
-  <si>
-    <t>Profile screen loads fields for user settings adjustments</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-APP-24</t>
-  </si>
-  <si>
-    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
-  </si>
-  <si>
-    <t>Display Name changes update the user info values on Save</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-APP-25</t>
-  </si>
-  <si>
-    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
-  </si>
-  <si>
-    <t>Preferred currency symbol alters default currency label layout</t>
-  </si>
-  <si>
-    <t>TC-APP-26</t>
-  </si>
-  <si>
-    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
-  </si>
-  <si>
-    <t>Dialog queries permissions access to camera device for receipts scan</t>
-  </si>
-  <si>
-    <t>TC-APP-27</t>
-  </si>
-  <si>
-    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
-  </si>
-  <si>
-    <t>Toggling dark theme alters app styling variables colors</t>
-  </si>
-  <si>
-    <t>TC-APP-28</t>
-  </si>
-  <si>
-    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
-  </si>
-  <si>
-    <t>Logout prompts verification warning dialog</t>
-  </si>
-  <si>
-    <t>TC-APP-29</t>
-  </si>
-  <si>
-    <t>TC-APP-29: Verify double tap mobile back button exits the application safely</t>
-  </si>
-  <si>
-    <t>Double tap exits execution thread and backgrounds app</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-APP-30</t>
-  </si>
-  <si>
-    <t>TC-APP-30: Verify complete authentication details and cached tokens wipe on Logout</t>
-  </si>
-  <si>
-    <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1459,21 +1450,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1482,21 +1473,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1505,21 +1496,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1528,21 +1519,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1551,21 +1542,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1574,21 +1565,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1597,21 +1588,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1620,21 +1611,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1643,21 +1634,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1666,21 +1657,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1689,21 +1680,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1712,21 +1703,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1735,21 +1726,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1758,21 +1749,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1781,21 +1772,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1804,21 +1795,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1827,21 +1818,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1850,21 +1841,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1873,21 +1864,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1896,7 +1887,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1928,27 +1919,27 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1971,19 +1962,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1991,16 +1982,16 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2008,16 +1999,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2025,16 +2016,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2059,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2076,16 +2067,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2093,16 +2084,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2110,16 +2101,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2127,16 +2118,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2161,16 +2152,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2178,16 +2169,16 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2195,16 +2186,16 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2212,16 +2203,16 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2263,16 +2254,16 @@
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2280,16 +2271,16 @@
         <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2297,16 +2288,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2348,16 +2339,16 @@
         <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2382,16 +2373,16 @@
         <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2433,16 +2424,16 @@
         <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2450,16 +2441,16 @@
         <v>3</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2467,16 +2458,16 @@
         <v>3</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2484,16 +2475,16 @@
         <v>3</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2501,16 +2492,16 @@
         <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2518,16 +2509,16 @@
         <v>3</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2569,16 +2560,16 @@
         <v>3</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2589,7 +2580,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -2603,16 +2594,16 @@
         <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2620,16 +2611,16 @@
         <v>3</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2637,16 +2628,16 @@
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2654,16 +2645,16 @@
         <v>3</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2671,16 +2662,16 @@
         <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2688,16 +2679,16 @@
         <v>3</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2708,7 +2699,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
@@ -2725,7 +2716,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
@@ -2742,7 +2733,7 @@
         <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
@@ -2756,16 +2747,16 @@
         <v>3</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2776,7 +2767,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
@@ -2790,16 +2781,16 @@
         <v>3</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2807,16 +2798,16 @@
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2824,16 +2815,16 @@
         <v>3</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2841,16 +2832,16 @@
         <v>3</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2858,16 +2849,16 @@
         <v>3</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2878,7 +2869,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
@@ -2892,16 +2883,16 @@
         <v>3</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2909,16 +2900,16 @@
         <v>3</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2926,16 +2917,16 @@
         <v>3</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2943,16 +2934,16 @@
         <v>3</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,16 +2951,16 @@
         <v>3</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2977,16 +2968,16 @@
         <v>3</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2994,16 +2985,16 @@
         <v>3</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3011,16 +3002,16 @@
         <v>3</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3028,16 +3019,16 @@
         <v>3</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3045,16 +3036,16 @@
         <v>3</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3065,7 +3056,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
@@ -3082,7 +3073,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
@@ -3099,7 +3090,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
@@ -3116,7 +3107,7 @@
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3133,7 +3124,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
@@ -3147,16 +3138,16 @@
         <v>3</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3167,7 +3158,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3181,16 +3172,16 @@
         <v>3</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3198,16 +3189,16 @@
         <v>3</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3215,16 +3206,16 @@
         <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3232,16 +3223,16 @@
         <v>3</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3249,16 +3240,16 @@
         <v>3</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3269,7 +3260,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3283,16 +3274,16 @@
         <v>3</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3300,16 +3291,16 @@
         <v>3</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3317,16 +3308,16 @@
         <v>3</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3334,16 +3325,16 @@
         <v>3</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3354,7 +3345,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3371,7 +3362,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3388,7 +3379,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
@@ -3405,7 +3396,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
@@ -3422,7 +3413,7 @@
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
@@ -3436,16 +3427,16 @@
         <v>3</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3456,7 +3447,7 @@
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="208">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 5:48:31 AM</t>
+    <t>6/16/2026, 5:54:26 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.86s</t>
+    <t>9.55s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,261 +103,273 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-APP-02</t>
+  </si>
+  <si>
+    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
+  </si>
+  <si>
+    <t>App prevents submission on empty email or password fields</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-APP-03</t>
+  </si>
+  <si>
+    <t>TC-APP-03: Validate login email address format checking rules</t>
+  </si>
+  <si>
+    <t>Error label displays when email format is invalid</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-APP-04</t>
+  </si>
+  <si>
+    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
+  </si>
+  <si>
+    <t>App registers biometric device setup option in local state</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-APP-05</t>
+  </si>
+  <si>
+    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
+  </si>
+  <si>
+    <t>Dashboard balance, income, and expense summary widgets render</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-APP-06</t>
+  </si>
+  <si>
+    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
+  </si>
+  <si>
+    <t>Balance summary card resolves within view limits</t>
+  </si>
+  <si>
     <t>0.23s</t>
   </si>
   <si>
-    <t>TC-APP-02</t>
-  </si>
-  <si>
-    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
-  </si>
-  <si>
-    <t>App prevents submission on empty email or password fields</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-APP-03</t>
-  </si>
-  <si>
-    <t>TC-APP-03: Validate login email address format checking rules</t>
-  </si>
-  <si>
-    <t>Error label displays when email format is invalid</t>
+    <t>TC-APP-07</t>
+  </si>
+  <si>
+    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
+  </si>
+  <si>
+    <t>Pull to refresh updates transaction listings from background storage</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-APP-08</t>
+  </si>
+  <si>
+    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
+  </si>
+  <si>
+    <t>Income sheet modal slides into view</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-APP-09</t>
+  </si>
+  <si>
+    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
+  </si>
+  <si>
+    <t>Category select holds Salary, Freelance, and Investments options</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-APP-10</t>
+  </si>
+  <si>
+    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
+  </si>
+  <si>
+    <t>Income fields accept numeric and descriptive inputs</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-APP-11</t>
+  </si>
+  <si>
+    <t>TC-APP-11: Validate empty income form submission error indicators</t>
+  </si>
+  <si>
+    <t>Missing amount triggers mobile error highlights</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-APP-12</t>
+  </si>
+  <si>
+    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
+  </si>
+  <si>
+    <t>Expense sheet slides up with focus on Category dropdown</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-APP-13</t>
+  </si>
+  <si>
+    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
+  </si>
+  <si>
+    <t>Expense logging works and decreases overall dashboard balance</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-APP-14</t>
+  </si>
+  <si>
+    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
+  </si>
+  <si>
+    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
+  </si>
+  <si>
+    <t>TC-APP-15</t>
+  </si>
+  <si>
+    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
+  </si>
+  <si>
+    <t>Soft keyboard changes to numeric layout on amount field focus</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-APP-16</t>
+  </si>
+  <si>
+    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
+  </si>
+  <si>
+    <t>Active budget progress limiters are visible</t>
+  </si>
+  <si>
+    <t>TC-APP-17</t>
+  </si>
+  <si>
+    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
+  </si>
+  <si>
+    <t>Progress bar limits adjust to new budget configurations</t>
+  </si>
+  <si>
+    <t>TC-APP-18</t>
+  </si>
+  <si>
+    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
+  </si>
+  <si>
+    <t>Alert popup loads when transaction breaches designated cap threshold</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-APP-19</t>
+  </si>
+  <si>
+    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
+  </si>
+  <si>
+    <t>Distribution chart switches between absolute values and percentages</t>
+  </si>
+  <si>
+    <t>TC-APP-20</t>
+  </si>
+  <si>
+    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
+  </si>
+  <si>
+    <t>Push alert fires sending current limits allocations reminders</t>
+  </si>
+  <si>
+    <t>0.48s</t>
+  </si>
+  <si>
+    <t>TC-APP-21</t>
+  </si>
+  <si>
+    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
+  </si>
+  <si>
+    <t>Successful transactions prompt immediate mobile success toast alert</t>
+  </si>
+  <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-APP-22</t>
+  </si>
+  <si>
+    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
+  </si>
+  <si>
+    <t>Swiping a notification alert row removes it from notifications panel</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-APP-23</t>
+  </si>
+  <si>
+    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
+  </si>
+  <si>
+    <t>Profile screen loads fields for user settings adjustments</t>
   </si>
   <si>
     <t>0.42s</t>
   </si>
   <si>
-    <t>TC-APP-04</t>
-  </si>
-  <si>
-    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
-  </si>
-  <si>
-    <t>App registers biometric device setup option in local state</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-APP-05</t>
-  </si>
-  <si>
-    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
-  </si>
-  <si>
-    <t>Dashboard balance, income, and expense summary widgets render</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-APP-06</t>
-  </si>
-  <si>
-    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
-  </si>
-  <si>
-    <t>Balance summary card resolves within view limits</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-APP-07</t>
-  </si>
-  <si>
-    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
-  </si>
-  <si>
-    <t>Pull to refresh updates transaction listings from background storage</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-APP-08</t>
-  </si>
-  <si>
-    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
-  </si>
-  <si>
-    <t>Income sheet modal slides into view</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-APP-09</t>
-  </si>
-  <si>
-    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
-  </si>
-  <si>
-    <t>Category select holds Salary, Freelance, and Investments options</t>
-  </si>
-  <si>
-    <t>0.47s</t>
-  </si>
-  <si>
-    <t>TC-APP-10</t>
-  </si>
-  <si>
-    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
-  </si>
-  <si>
-    <t>Income fields accept numeric and descriptive inputs</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
-    <t>TC-APP-11</t>
-  </si>
-  <si>
-    <t>TC-APP-11: Validate empty income form submission error indicators</t>
-  </si>
-  <si>
-    <t>Missing amount triggers mobile error highlights</t>
-  </si>
-  <si>
-    <t>TC-APP-12</t>
-  </si>
-  <si>
-    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
-  </si>
-  <si>
-    <t>Expense sheet slides up with focus on Category dropdown</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-APP-13</t>
-  </si>
-  <si>
-    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
-  </si>
-  <si>
-    <t>Expense logging works and decreases overall dashboard balance</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-APP-14</t>
-  </si>
-  <si>
-    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
-  </si>
-  <si>
-    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
-  </si>
-  <si>
-    <t>TC-APP-15</t>
-  </si>
-  <si>
-    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
-  </si>
-  <si>
-    <t>Soft keyboard changes to numeric layout on amount field focus</t>
-  </si>
-  <si>
-    <t>TC-APP-16</t>
-  </si>
-  <si>
-    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
-  </si>
-  <si>
-    <t>Active budget progress limiters are visible</t>
-  </si>
-  <si>
-    <t>TC-APP-17</t>
-  </si>
-  <si>
-    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
-  </si>
-  <si>
-    <t>Progress bar limits adjust to new budget configurations</t>
-  </si>
-  <si>
-    <t>TC-APP-18</t>
-  </si>
-  <si>
-    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
-  </si>
-  <si>
-    <t>Alert popup loads when transaction breaches designated cap threshold</t>
-  </si>
-  <si>
-    <t>TC-APP-19</t>
-  </si>
-  <si>
-    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
-  </si>
-  <si>
-    <t>Distribution chart switches between absolute values and percentages</t>
-  </si>
-  <si>
-    <t>TC-APP-20</t>
-  </si>
-  <si>
-    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
-  </si>
-  <si>
-    <t>Push alert fires sending current limits allocations reminders</t>
-  </si>
-  <si>
-    <t>TC-APP-21</t>
-  </si>
-  <si>
-    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
-  </si>
-  <si>
-    <t>Successful transactions prompt immediate mobile success toast alert</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-APP-22</t>
-  </si>
-  <si>
-    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
-  </si>
-  <si>
-    <t>Swiping a notification alert row removes it from notifications panel</t>
+    <t>TC-APP-24</t>
+  </si>
+  <si>
+    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
+  </si>
+  <si>
+    <t>Display Name changes update the user info values on Save</t>
   </si>
   <si>
     <t>0.17s</t>
   </si>
   <si>
-    <t>TC-APP-23</t>
-  </si>
-  <si>
-    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
-  </si>
-  <si>
-    <t>Profile screen loads fields for user settings adjustments</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-APP-24</t>
-  </si>
-  <si>
-    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
-  </si>
-  <si>
-    <t>Display Name changes update the user info values on Save</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
     <t>TC-APP-25</t>
   </si>
   <si>
@@ -367,9 +379,6 @@
     <t>Preferred currency symbol alters default currency label layout</t>
   </si>
   <si>
-    <t>0.19s</t>
-  </si>
-  <si>
     <t>TC-APP-26</t>
   </si>
   <si>
@@ -388,6 +397,9 @@
     <t>Toggling dark theme alters app styling variables colors</t>
   </si>
   <si>
+    <t>0.35s</t>
+  </si>
+  <si>
     <t>TC-APP-28</t>
   </si>
   <si>
@@ -397,9 +409,6 @@
     <t>Logout prompts verification warning dialog</t>
   </si>
   <si>
-    <t>0.13s</t>
-  </si>
-  <si>
     <t>TC-APP-29</t>
   </si>
   <si>
@@ -416,9 +425,6 @@
   </si>
   <si>
     <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
-  </si>
-  <si>
-    <t>0.21s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1450,21 +1456,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1473,21 +1479,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1496,21 +1502,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1519,21 +1525,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1542,21 +1548,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1565,21 +1571,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1588,21 +1594,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1611,21 +1617,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1634,21 +1640,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1657,21 +1663,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1680,21 +1686,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1703,21 +1709,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1726,21 +1732,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1749,21 +1755,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1772,21 +1778,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1795,21 +1801,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1818,21 +1824,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1841,21 +1847,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1864,21 +1870,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>41</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1887,7 +1893,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1919,27 +1925,27 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1962,19 +1968,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1982,16 +1988,16 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1999,16 +2005,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2016,16 +2022,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2050,16 +2056,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2067,16 +2073,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2084,16 +2090,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2101,16 +2107,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2118,16 +2124,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2152,16 +2158,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2169,16 +2175,16 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2186,16 +2192,16 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2203,16 +2209,16 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2254,16 +2260,16 @@
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2271,16 +2277,16 @@
         <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2288,16 +2294,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2339,16 +2345,16 @@
         <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2373,16 +2379,16 @@
         <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2424,16 +2430,16 @@
         <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2441,16 +2447,16 @@
         <v>3</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2458,16 +2464,16 @@
         <v>3</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2475,16 +2481,16 @@
         <v>3</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2492,16 +2498,16 @@
         <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2509,16 +2515,16 @@
         <v>3</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2560,16 +2566,16 @@
         <v>3</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2580,7 +2586,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -2594,16 +2600,16 @@
         <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2611,16 +2617,16 @@
         <v>3</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2628,16 +2634,16 @@
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2645,16 +2651,16 @@
         <v>3</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2662,16 +2668,16 @@
         <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2679,16 +2685,16 @@
         <v>3</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2699,7 +2705,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
@@ -2716,7 +2722,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
@@ -2733,7 +2739,7 @@
         <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
@@ -2747,16 +2753,16 @@
         <v>3</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2767,7 +2773,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
@@ -2781,16 +2787,16 @@
         <v>3</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2798,16 +2804,16 @@
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2815,16 +2821,16 @@
         <v>3</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2832,16 +2838,16 @@
         <v>3</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2849,16 +2855,16 @@
         <v>3</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2869,7 +2875,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
@@ -2883,16 +2889,16 @@
         <v>3</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2900,16 +2906,16 @@
         <v>3</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2917,16 +2923,16 @@
         <v>3</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2934,16 +2940,16 @@
         <v>3</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2951,16 +2957,16 @@
         <v>3</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2968,16 +2974,16 @@
         <v>3</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2985,16 +2991,16 @@
         <v>3</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3002,16 +3008,16 @@
         <v>3</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3019,16 +3025,16 @@
         <v>3</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3036,16 +3042,16 @@
         <v>3</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3056,7 +3062,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
@@ -3073,7 +3079,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
@@ -3090,7 +3096,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
@@ -3107,7 +3113,7 @@
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3124,7 +3130,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
@@ -3138,16 +3144,16 @@
         <v>3</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3158,7 +3164,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3172,16 +3178,16 @@
         <v>3</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3189,16 +3195,16 @@
         <v>3</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3206,16 +3212,16 @@
         <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3223,16 +3229,16 @@
         <v>3</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3240,16 +3246,16 @@
         <v>3</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3260,7 +3266,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3274,16 +3280,16 @@
         <v>3</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3291,16 +3297,16 @@
         <v>3</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3308,16 +3314,16 @@
         <v>3</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3325,16 +3331,16 @@
         <v>3</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3345,7 +3351,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3362,7 +3368,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3379,7 +3385,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
@@ -3396,7 +3402,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
@@ -3413,7 +3419,7 @@
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
@@ -3427,16 +3433,16 @@
         <v>3</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3447,7 +3453,7 @@
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="209">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 7:30:55 AM</t>
+    <t>6/16/2026, 7:34:38 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>9.31s</t>
+    <t>9.10s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,249 +103,249 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-APP-02</t>
+  </si>
+  <si>
+    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
+  </si>
+  <si>
+    <t>App prevents submission on empty email or password fields</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-APP-03</t>
+  </si>
+  <si>
+    <t>TC-APP-03: Validate login email address format checking rules</t>
+  </si>
+  <si>
+    <t>Error label displays when email format is invalid</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-APP-04</t>
+  </si>
+  <si>
+    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
+  </si>
+  <si>
+    <t>App registers biometric device setup option in local state</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-APP-05</t>
+  </si>
+  <si>
+    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
+  </si>
+  <si>
+    <t>Dashboard balance, income, and expense summary widgets render</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-APP-06</t>
+  </si>
+  <si>
+    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
+  </si>
+  <si>
+    <t>Balance summary card resolves within view limits</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-APP-07</t>
+  </si>
+  <si>
+    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
+  </si>
+  <si>
+    <t>Pull to refresh updates transaction listings from background storage</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-APP-08</t>
+  </si>
+  <si>
+    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
+  </si>
+  <si>
+    <t>Income sheet modal slides into view</t>
+  </si>
+  <si>
+    <t>TC-APP-09</t>
+  </si>
+  <si>
+    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
+  </si>
+  <si>
+    <t>Category select holds Salary, Freelance, and Investments options</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-APP-10</t>
+  </si>
+  <si>
+    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
+  </si>
+  <si>
+    <t>Income fields accept numeric and descriptive inputs</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-APP-11</t>
+  </si>
+  <si>
+    <t>TC-APP-11: Validate empty income form submission error indicators</t>
+  </si>
+  <si>
+    <t>Missing amount triggers mobile error highlights</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-APP-12</t>
+  </si>
+  <si>
+    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
+  </si>
+  <si>
+    <t>Expense sheet slides up with focus on Category dropdown</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-APP-13</t>
+  </si>
+  <si>
+    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
+  </si>
+  <si>
+    <t>Expense logging works and decreases overall dashboard balance</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-APP-14</t>
+  </si>
+  <si>
+    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
+  </si>
+  <si>
+    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-APP-15</t>
+  </si>
+  <si>
+    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
+  </si>
+  <si>
+    <t>Soft keyboard changes to numeric layout on amount field focus</t>
+  </si>
+  <si>
+    <t>TC-APP-16</t>
+  </si>
+  <si>
+    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
+  </si>
+  <si>
+    <t>Active budget progress limiters are visible</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-APP-17</t>
+  </si>
+  <si>
+    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
+  </si>
+  <si>
+    <t>Progress bar limits adjust to new budget configurations</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-APP-18</t>
+  </si>
+  <si>
+    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
+  </si>
+  <si>
+    <t>Alert popup loads when transaction breaches designated cap threshold</t>
+  </si>
+  <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-APP-19</t>
+  </si>
+  <si>
+    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
+  </si>
+  <si>
+    <t>Distribution chart switches between absolute values and percentages</t>
+  </si>
+  <si>
+    <t>TC-APP-20</t>
+  </si>
+  <si>
+    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
+  </si>
+  <si>
+    <t>Push alert fires sending current limits allocations reminders</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-APP-21</t>
+  </si>
+  <si>
+    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
+  </si>
+  <si>
+    <t>Successful transactions prompt immediate mobile success toast alert</t>
+  </si>
+  <si>
+    <t>TC-APP-22</t>
+  </si>
+  <si>
+    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
+  </si>
+  <si>
+    <t>Swiping a notification alert row removes it from notifications panel</t>
+  </si>
+  <si>
     <t>0.45s</t>
   </si>
   <si>
-    <t>TC-APP-02</t>
-  </si>
-  <si>
-    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
-  </si>
-  <si>
-    <t>App prevents submission on empty email or password fields</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-APP-03</t>
-  </si>
-  <si>
-    <t>TC-APP-03: Validate login email address format checking rules</t>
-  </si>
-  <si>
-    <t>Error label displays when email format is invalid</t>
-  </si>
-  <si>
-    <t>0.47s</t>
-  </si>
-  <si>
-    <t>TC-APP-04</t>
-  </si>
-  <si>
-    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
-  </si>
-  <si>
-    <t>App registers biometric device setup option in local state</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-APP-05</t>
-  </si>
-  <si>
-    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
-  </si>
-  <si>
-    <t>Dashboard balance, income, and expense summary widgets render</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-APP-06</t>
-  </si>
-  <si>
-    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
-  </si>
-  <si>
-    <t>Balance summary card resolves within view limits</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-APP-07</t>
-  </si>
-  <si>
-    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
-  </si>
-  <si>
-    <t>Pull to refresh updates transaction listings from background storage</t>
-  </si>
-  <si>
-    <t>TC-APP-08</t>
-  </si>
-  <si>
-    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
-  </si>
-  <si>
-    <t>Income sheet modal slides into view</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-APP-09</t>
-  </si>
-  <si>
-    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
-  </si>
-  <si>
-    <t>Category select holds Salary, Freelance, and Investments options</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-APP-10</t>
-  </si>
-  <si>
-    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
-  </si>
-  <si>
-    <t>Income fields accept numeric and descriptive inputs</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-APP-11</t>
-  </si>
-  <si>
-    <t>TC-APP-11: Validate empty income form submission error indicators</t>
-  </si>
-  <si>
-    <t>Missing amount triggers mobile error highlights</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-APP-12</t>
-  </si>
-  <si>
-    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
-  </si>
-  <si>
-    <t>Expense sheet slides up with focus on Category dropdown</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-APP-13</t>
-  </si>
-  <si>
-    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
-  </si>
-  <si>
-    <t>Expense logging works and decreases overall dashboard balance</t>
-  </si>
-  <si>
-    <t>TC-APP-14</t>
-  </si>
-  <si>
-    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
-  </si>
-  <si>
-    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
-  </si>
-  <si>
-    <t>TC-APP-15</t>
-  </si>
-  <si>
-    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
-  </si>
-  <si>
-    <t>Soft keyboard changes to numeric layout on amount field focus</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-APP-16</t>
-  </si>
-  <si>
-    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
-  </si>
-  <si>
-    <t>Active budget progress limiters are visible</t>
-  </si>
-  <si>
-    <t>TC-APP-17</t>
-  </si>
-  <si>
-    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
-  </si>
-  <si>
-    <t>Progress bar limits adjust to new budget configurations</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-APP-18</t>
-  </si>
-  <si>
-    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
-  </si>
-  <si>
-    <t>Alert popup loads when transaction breaches designated cap threshold</t>
-  </si>
-  <si>
-    <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-APP-19</t>
-  </si>
-  <si>
-    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
-  </si>
-  <si>
-    <t>Distribution chart switches between absolute values and percentages</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-APP-20</t>
-  </si>
-  <si>
-    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
-  </si>
-  <si>
-    <t>Push alert fires sending current limits allocations reminders</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-APP-21</t>
-  </si>
-  <si>
-    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
-  </si>
-  <si>
-    <t>Successful transactions prompt immediate mobile success toast alert</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-APP-22</t>
-  </si>
-  <si>
-    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
-  </si>
-  <si>
-    <t>Swiping a notification alert row removes it from notifications panel</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
     <t>TC-APP-23</t>
   </si>
   <si>
@@ -355,9 +355,6 @@
     <t>Profile screen loads fields for user settings adjustments</t>
   </si>
   <si>
-    <t>0.30s</t>
-  </si>
-  <si>
     <t>TC-APP-24</t>
   </si>
   <si>
@@ -367,7 +364,7 @@
     <t>Display Name changes update the user info values on Save</t>
   </si>
   <si>
-    <t>0.14s</t>
+    <t>0.34s</t>
   </si>
   <si>
     <t>TC-APP-25</t>
@@ -397,7 +394,7 @@
     <t>Toggling dark theme alters app styling variables colors</t>
   </si>
   <si>
-    <t>0.38s</t>
+    <t>0.48s</t>
   </si>
   <si>
     <t>TC-APP-28</t>
@@ -409,6 +406,9 @@
     <t>Logout prompts verification warning dialog</t>
   </si>
   <si>
+    <t>0.35s</t>
+  </si>
+  <si>
     <t>TC-APP-29</t>
   </si>
   <si>
@@ -418,9 +418,6 @@
     <t>Double tap exits execution thread and backgrounds app</t>
   </si>
   <si>
-    <t>0.35s</t>
-  </si>
-  <si>
     <t>TC-APP-30</t>
   </si>
   <si>
@@ -430,7 +427,7 @@
     <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
   </si>
   <si>
-    <t>0.33s</t>
+    <t>0.46s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1370,21 +1367,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1393,7 +1390,7 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1508,21 +1505,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1531,21 +1528,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1554,21 +1551,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1577,21 +1574,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1600,21 +1597,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1623,21 +1620,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1646,21 +1643,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1669,21 +1666,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1692,7 +1689,7 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1738,21 +1735,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1761,21 +1758,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1784,21 +1781,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1812,16 +1809,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1830,21 +1827,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1853,7 +1850,7 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1876,21 +1873,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>134</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1899,7 +1896,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1931,27 +1928,27 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1974,19 +1971,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1994,16 +1991,16 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2011,16 +2008,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2028,16 +2025,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2062,16 +2059,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2079,16 +2076,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2096,16 +2093,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2113,16 +2110,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2130,16 +2127,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2164,16 +2161,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2181,16 +2178,16 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2198,16 +2195,16 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2215,16 +2212,16 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2266,16 +2263,16 @@
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2283,16 +2280,16 @@
         <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2300,16 +2297,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2351,16 +2348,16 @@
         <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2385,16 +2382,16 @@
         <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2405,7 +2402,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2436,16 +2433,16 @@
         <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2453,16 +2450,16 @@
         <v>3</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2470,16 +2467,16 @@
         <v>3</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2487,16 +2484,16 @@
         <v>3</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2504,16 +2501,16 @@
         <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2521,16 +2518,16 @@
         <v>3</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2572,16 +2569,16 @@
         <v>3</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2606,16 +2603,16 @@
         <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2623,16 +2620,16 @@
         <v>3</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2640,16 +2637,16 @@
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2657,16 +2654,16 @@
         <v>3</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2674,16 +2671,16 @@
         <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2691,16 +2688,16 @@
         <v>3</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2728,7 +2725,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
@@ -2745,7 +2742,7 @@
         <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
@@ -2759,16 +2756,16 @@
         <v>3</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2779,7 +2776,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
@@ -2793,16 +2790,16 @@
         <v>3</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2810,16 +2807,16 @@
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2827,16 +2824,16 @@
         <v>3</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2844,16 +2841,16 @@
         <v>3</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2861,16 +2858,16 @@
         <v>3</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2881,7 +2878,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
@@ -2895,16 +2892,16 @@
         <v>3</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2912,16 +2909,16 @@
         <v>3</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C56" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2929,16 +2926,16 @@
         <v>3</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2946,16 +2943,16 @@
         <v>3</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2963,16 +2960,16 @@
         <v>3</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2980,16 +2977,16 @@
         <v>3</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2997,16 +2994,16 @@
         <v>3</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3014,16 +3011,16 @@
         <v>3</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3031,16 +3028,16 @@
         <v>3</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3048,16 +3045,16 @@
         <v>3</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3068,7 +3065,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
@@ -3085,7 +3082,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
@@ -3102,7 +3099,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
@@ -3119,7 +3116,7 @@
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3150,16 +3147,16 @@
         <v>3</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3184,16 +3181,16 @@
         <v>3</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3201,16 +3198,16 @@
         <v>3</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3218,16 +3215,16 @@
         <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3235,16 +3232,16 @@
         <v>3</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3252,16 +3249,16 @@
         <v>3</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3272,7 +3269,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3286,16 +3283,16 @@
         <v>3</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3303,16 +3300,16 @@
         <v>3</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C79" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3320,16 +3317,16 @@
         <v>3</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3337,16 +3334,16 @@
         <v>3</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3357,7 +3354,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3374,7 +3371,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3391,7 +3388,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
@@ -3408,7 +3405,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
@@ -3439,16 +3436,16 @@
         <v>3</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="D87" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3459,7 +3456,7 @@
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="206">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 7:30:55 AM</t>
+    <t>6/18/2026, 4:42:18 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>9.31s</t>
+    <t>8.43s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.45s</t>
+    <t>0.26s</t>
   </si>
   <si>
     <t>TC-APP-02</t>
@@ -115,7 +115,7 @@
     <t>App prevents submission on empty email or password fields</t>
   </si>
   <si>
-    <t>0.26s</t>
+    <t>0.12s</t>
   </si>
   <si>
     <t>TC-APP-03</t>
@@ -127,7 +127,7 @@
     <t>Error label displays when email format is invalid</t>
   </si>
   <si>
-    <t>0.47s</t>
+    <t>0.17s</t>
   </si>
   <si>
     <t>TC-APP-04</t>
@@ -139,7 +139,7 @@
     <t>App registers biometric device setup option in local state</t>
   </si>
   <si>
-    <t>0.32s</t>
+    <t>0.42s</t>
   </si>
   <si>
     <t>TC-APP-05</t>
@@ -151,286 +151,274 @@
     <t>Dashboard balance, income, and expense summary widgets render</t>
   </si>
   <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-APP-06</t>
+  </si>
+  <si>
+    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
+  </si>
+  <si>
+    <t>Balance summary card resolves within view limits</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-APP-07</t>
+  </si>
+  <si>
+    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
+  </si>
+  <si>
+    <t>Pull to refresh updates transaction listings from background storage</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-APP-08</t>
+  </si>
+  <si>
+    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
+  </si>
+  <si>
+    <t>Income sheet modal slides into view</t>
+  </si>
+  <si>
+    <t>TC-APP-09</t>
+  </si>
+  <si>
+    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
+  </si>
+  <si>
+    <t>Category select holds Salary, Freelance, and Investments options</t>
+  </si>
+  <si>
+    <t>TC-APP-10</t>
+  </si>
+  <si>
+    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
+  </si>
+  <si>
+    <t>Income fields accept numeric and descriptive inputs</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-APP-11</t>
+  </si>
+  <si>
+    <t>TC-APP-11: Validate empty income form submission error indicators</t>
+  </si>
+  <si>
+    <t>Missing amount triggers mobile error highlights</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-APP-12</t>
+  </si>
+  <si>
+    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
+  </si>
+  <si>
+    <t>Expense sheet slides up with focus on Category dropdown</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-APP-13</t>
+  </si>
+  <si>
+    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
+  </si>
+  <si>
+    <t>Expense logging works and decreases overall dashboard balance</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-APP-14</t>
+  </si>
+  <si>
+    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
+  </si>
+  <si>
+    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
+  </si>
+  <si>
+    <t>TC-APP-15</t>
+  </si>
+  <si>
+    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
+  </si>
+  <si>
+    <t>Soft keyboard changes to numeric layout on amount field focus</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-APP-16</t>
+  </si>
+  <si>
+    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
+  </si>
+  <si>
+    <t>Active budget progress limiters are visible</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-APP-17</t>
+  </si>
+  <si>
+    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
+  </si>
+  <si>
+    <t>Progress bar limits adjust to new budget configurations</t>
+  </si>
+  <si>
+    <t>TC-APP-18</t>
+  </si>
+  <si>
+    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
+  </si>
+  <si>
+    <t>Alert popup loads when transaction breaches designated cap threshold</t>
+  </si>
+  <si>
+    <t>TC-APP-19</t>
+  </si>
+  <si>
+    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
+  </si>
+  <si>
+    <t>Distribution chart switches between absolute values and percentages</t>
+  </si>
+  <si>
     <t>0.22s</t>
   </si>
   <si>
-    <t>TC-APP-06</t>
-  </si>
-  <si>
-    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
-  </si>
-  <si>
-    <t>Balance summary card resolves within view limits</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-APP-07</t>
-  </si>
-  <si>
-    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
-  </si>
-  <si>
-    <t>Pull to refresh updates transaction listings from background storage</t>
-  </si>
-  <si>
-    <t>TC-APP-08</t>
-  </si>
-  <si>
-    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
-  </si>
-  <si>
-    <t>Income sheet modal slides into view</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-APP-09</t>
-  </si>
-  <si>
-    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
-  </si>
-  <si>
-    <t>Category select holds Salary, Freelance, and Investments options</t>
+    <t>TC-APP-20</t>
+  </si>
+  <si>
+    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
+  </si>
+  <si>
+    <t>Push alert fires sending current limits allocations reminders</t>
   </si>
   <si>
     <t>0.39s</t>
   </si>
   <si>
-    <t>TC-APP-10</t>
-  </si>
-  <si>
-    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
-  </si>
-  <si>
-    <t>Income fields accept numeric and descriptive inputs</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-APP-11</t>
-  </si>
-  <si>
-    <t>TC-APP-11: Validate empty income form submission error indicators</t>
-  </si>
-  <si>
-    <t>Missing amount triggers mobile error highlights</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-APP-12</t>
-  </si>
-  <si>
-    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
-  </si>
-  <si>
-    <t>Expense sheet slides up with focus on Category dropdown</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-APP-13</t>
-  </si>
-  <si>
-    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
-  </si>
-  <si>
-    <t>Expense logging works and decreases overall dashboard balance</t>
-  </si>
-  <si>
-    <t>TC-APP-14</t>
-  </si>
-  <si>
-    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
-  </si>
-  <si>
-    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
-  </si>
-  <si>
-    <t>TC-APP-15</t>
-  </si>
-  <si>
-    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
-  </si>
-  <si>
-    <t>Soft keyboard changes to numeric layout on amount field focus</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-APP-16</t>
-  </si>
-  <si>
-    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
-  </si>
-  <si>
-    <t>Active budget progress limiters are visible</t>
-  </si>
-  <si>
-    <t>TC-APP-17</t>
-  </si>
-  <si>
-    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
-  </si>
-  <si>
-    <t>Progress bar limits adjust to new budget configurations</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-APP-18</t>
-  </si>
-  <si>
-    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
-  </si>
-  <si>
-    <t>Alert popup loads when transaction breaches designated cap threshold</t>
+    <t>TC-APP-21</t>
+  </si>
+  <si>
+    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
+  </si>
+  <si>
+    <t>Successful transactions prompt immediate mobile success toast alert</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-APP-22</t>
+  </si>
+  <si>
+    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
+  </si>
+  <si>
+    <t>Swiping a notification alert row removes it from notifications panel</t>
+  </si>
+  <si>
+    <t>TC-APP-23</t>
+  </si>
+  <si>
+    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
+  </si>
+  <si>
+    <t>Profile screen loads fields for user settings adjustments</t>
+  </si>
+  <si>
+    <t>TC-APP-24</t>
+  </si>
+  <si>
+    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
+  </si>
+  <si>
+    <t>Display Name changes update the user info values on Save</t>
+  </si>
+  <si>
+    <t>TC-APP-25</t>
+  </si>
+  <si>
+    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
+  </si>
+  <si>
+    <t>Preferred currency symbol alters default currency label layout</t>
+  </si>
+  <si>
+    <t>TC-APP-26</t>
+  </si>
+  <si>
+    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
+  </si>
+  <si>
+    <t>Dialog queries permissions access to camera device for receipts scan</t>
+  </si>
+  <si>
+    <t>TC-APP-27</t>
+  </si>
+  <si>
+    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
+  </si>
+  <si>
+    <t>Toggling dark theme alters app styling variables colors</t>
+  </si>
+  <si>
+    <t>TC-APP-28</t>
+  </si>
+  <si>
+    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
+  </si>
+  <si>
+    <t>Logout prompts verification warning dialog</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-APP-29</t>
+  </si>
+  <si>
+    <t>TC-APP-29: Verify double tap mobile back button exits the application safely</t>
+  </si>
+  <si>
+    <t>Double tap exits execution thread and backgrounds app</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-APP-30</t>
+  </si>
+  <si>
+    <t>TC-APP-30: Verify complete authentication details and cached tokens wipe on Logout</t>
+  </si>
+  <si>
+    <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
   </si>
   <si>
     <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-APP-19</t>
-  </si>
-  <si>
-    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
-  </si>
-  <si>
-    <t>Distribution chart switches between absolute values and percentages</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-APP-20</t>
-  </si>
-  <si>
-    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
-  </si>
-  <si>
-    <t>Push alert fires sending current limits allocations reminders</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-APP-21</t>
-  </si>
-  <si>
-    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
-  </si>
-  <si>
-    <t>Successful transactions prompt immediate mobile success toast alert</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-APP-22</t>
-  </si>
-  <si>
-    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
-  </si>
-  <si>
-    <t>Swiping a notification alert row removes it from notifications panel</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-APP-23</t>
-  </si>
-  <si>
-    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
-  </si>
-  <si>
-    <t>Profile screen loads fields for user settings adjustments</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-APP-24</t>
-  </si>
-  <si>
-    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
-  </si>
-  <si>
-    <t>Display Name changes update the user info values on Save</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-APP-25</t>
-  </si>
-  <si>
-    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
-  </si>
-  <si>
-    <t>Preferred currency symbol alters default currency label layout</t>
-  </si>
-  <si>
-    <t>TC-APP-26</t>
-  </si>
-  <si>
-    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
-  </si>
-  <si>
-    <t>Dialog queries permissions access to camera device for receipts scan</t>
-  </si>
-  <si>
-    <t>TC-APP-27</t>
-  </si>
-  <si>
-    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
-  </si>
-  <si>
-    <t>Toggling dark theme alters app styling variables colors</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-APP-28</t>
-  </si>
-  <si>
-    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
-  </si>
-  <si>
-    <t>Logout prompts verification warning dialog</t>
-  </si>
-  <si>
-    <t>TC-APP-29</t>
-  </si>
-  <si>
-    <t>TC-APP-29: Verify double tap mobile back button exits the application safely</t>
-  </si>
-  <si>
-    <t>Double tap exits execution thread and backgrounds app</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-APP-30</t>
-  </si>
-  <si>
-    <t>TC-APP-30: Verify complete authentication details and cached tokens wipe on Logout</t>
-  </si>
-  <si>
-    <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
-  </si>
-  <si>
-    <t>0.33s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1370,21 +1358,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1393,7 +1381,7 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1416,21 +1404,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1439,21 +1427,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1462,21 +1450,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1485,21 +1473,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1508,7 +1496,7 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1531,7 +1519,7 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1577,21 +1565,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1600,7 +1588,7 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1623,21 +1611,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1646,21 +1634,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1669,21 +1657,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1692,21 +1680,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1715,21 +1703,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1738,21 +1726,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1761,21 +1749,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1784,21 +1772,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1807,21 +1795,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1830,21 +1818,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1853,21 +1841,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1876,21 +1864,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1899,7 +1887,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1931,27 +1919,27 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1974,19 +1962,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1994,16 +1982,16 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2011,16 +1999,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2028,16 +2016,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2062,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2079,16 +2067,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2096,16 +2084,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2113,16 +2101,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2130,16 +2118,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2164,16 +2152,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2181,16 +2169,16 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2198,16 +2186,16 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2215,16 +2203,16 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2266,16 +2254,16 @@
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2283,16 +2271,16 @@
         <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2300,16 +2288,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2351,16 +2339,16 @@
         <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2385,16 +2373,16 @@
         <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2405,7 +2393,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2436,16 +2424,16 @@
         <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2453,16 +2441,16 @@
         <v>3</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2470,16 +2458,16 @@
         <v>3</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2487,16 +2475,16 @@
         <v>3</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2504,16 +2492,16 @@
         <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2521,16 +2509,16 @@
         <v>3</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2541,7 +2529,7 @@
         <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
@@ -2558,7 +2546,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
@@ -2572,16 +2560,16 @@
         <v>3</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2592,7 +2580,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -2606,16 +2594,16 @@
         <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2623,16 +2611,16 @@
         <v>3</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2640,16 +2628,16 @@
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2657,16 +2645,16 @@
         <v>3</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2674,16 +2662,16 @@
         <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2691,16 +2679,16 @@
         <v>3</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2711,7 +2699,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
@@ -2759,16 +2747,16 @@
         <v>3</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2793,16 +2781,16 @@
         <v>3</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2810,16 +2798,16 @@
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2827,16 +2815,16 @@
         <v>3</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2844,16 +2832,16 @@
         <v>3</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2861,16 +2849,16 @@
         <v>3</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2881,7 +2869,7 @@
         <v>24</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
@@ -2895,16 +2883,16 @@
         <v>3</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2912,16 +2900,16 @@
         <v>3</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2929,16 +2917,16 @@
         <v>3</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2946,16 +2934,16 @@
         <v>3</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2963,16 +2951,16 @@
         <v>3</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2980,16 +2968,16 @@
         <v>3</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2997,16 +2985,16 @@
         <v>3</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3014,16 +3002,16 @@
         <v>3</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3031,16 +3019,16 @@
         <v>3</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3048,16 +3036,16 @@
         <v>3</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3085,7 +3073,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
@@ -3102,7 +3090,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
@@ -3119,7 +3107,7 @@
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3136,7 +3124,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
@@ -3150,16 +3138,16 @@
         <v>3</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3170,7 +3158,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3184,16 +3172,16 @@
         <v>3</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3201,16 +3189,16 @@
         <v>3</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3218,16 +3206,16 @@
         <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3235,16 +3223,16 @@
         <v>3</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3252,16 +3240,16 @@
         <v>3</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3272,7 +3260,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3286,16 +3274,16 @@
         <v>3</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3303,16 +3291,16 @@
         <v>3</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3320,16 +3308,16 @@
         <v>3</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3337,16 +3325,16 @@
         <v>3</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3357,7 +3345,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3374,7 +3362,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3391,7 +3379,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
@@ -3408,7 +3396,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
@@ -3425,7 +3413,7 @@
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
@@ -3439,16 +3427,16 @@
         <v>3</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3459,7 +3447,7 @@
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="208">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/18/2026, 4:42:18 AM</t>
+    <t>6/18/2026, 5:58:09 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.43s</t>
+    <t>9.54s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,300 +103,312 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-APP-02</t>
+  </si>
+  <si>
+    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
+  </si>
+  <si>
+    <t>App prevents submission on empty email or password fields</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-APP-03</t>
+  </si>
+  <si>
+    <t>TC-APP-03: Validate login email address format checking rules</t>
+  </si>
+  <si>
+    <t>Error label displays when email format is invalid</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-APP-04</t>
+  </si>
+  <si>
+    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
+  </si>
+  <si>
+    <t>App registers biometric device setup option in local state</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-APP-05</t>
+  </si>
+  <si>
+    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
+  </si>
+  <si>
+    <t>Dashboard balance, income, and expense summary widgets render</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-APP-06</t>
+  </si>
+  <si>
+    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
+  </si>
+  <si>
+    <t>Balance summary card resolves within view limits</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-APP-07</t>
+  </si>
+  <si>
+    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
+  </si>
+  <si>
+    <t>Pull to refresh updates transaction listings from background storage</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-APP-08</t>
+  </si>
+  <si>
+    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
+  </si>
+  <si>
+    <t>Income sheet modal slides into view</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-APP-09</t>
+  </si>
+  <si>
+    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
+  </si>
+  <si>
+    <t>Category select holds Salary, Freelance, and Investments options</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-APP-10</t>
+  </si>
+  <si>
+    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
+  </si>
+  <si>
+    <t>Income fields accept numeric and descriptive inputs</t>
+  </si>
+  <si>
+    <t>TC-APP-11</t>
+  </si>
+  <si>
+    <t>TC-APP-11: Validate empty income form submission error indicators</t>
+  </si>
+  <si>
+    <t>Missing amount triggers mobile error highlights</t>
+  </si>
+  <si>
     <t>0.26s</t>
   </si>
   <si>
-    <t>TC-APP-02</t>
-  </si>
-  <si>
-    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
-  </si>
-  <si>
-    <t>App prevents submission on empty email or password fields</t>
+    <t>TC-APP-12</t>
+  </si>
+  <si>
+    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
+  </si>
+  <si>
+    <t>Expense sheet slides up with focus on Category dropdown</t>
+  </si>
+  <si>
+    <t>TC-APP-13</t>
+  </si>
+  <si>
+    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
+  </si>
+  <si>
+    <t>Expense logging works and decreases overall dashboard balance</t>
+  </si>
+  <si>
+    <t>TC-APP-14</t>
+  </si>
+  <si>
+    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
+  </si>
+  <si>
+    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-APP-15</t>
+  </si>
+  <si>
+    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
+  </si>
+  <si>
+    <t>Soft keyboard changes to numeric layout on amount field focus</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-APP-16</t>
+  </si>
+  <si>
+    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
+  </si>
+  <si>
+    <t>Active budget progress limiters are visible</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-APP-17</t>
+  </si>
+  <si>
+    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
+  </si>
+  <si>
+    <t>Progress bar limits adjust to new budget configurations</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-APP-18</t>
+  </si>
+  <si>
+    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
+  </si>
+  <si>
+    <t>Alert popup loads when transaction breaches designated cap threshold</t>
+  </si>
+  <si>
+    <t>TC-APP-19</t>
+  </si>
+  <si>
+    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
+  </si>
+  <si>
+    <t>Distribution chart switches between absolute values and percentages</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-APP-20</t>
+  </si>
+  <si>
+    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
+  </si>
+  <si>
+    <t>Push alert fires sending current limits allocations reminders</t>
+  </si>
+  <si>
+    <t>TC-APP-21</t>
+  </si>
+  <si>
+    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
+  </si>
+  <si>
+    <t>Successful transactions prompt immediate mobile success toast alert</t>
+  </si>
+  <si>
+    <t>TC-APP-22</t>
+  </si>
+  <si>
+    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
+  </si>
+  <si>
+    <t>Swiping a notification alert row removes it from notifications panel</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-APP-23</t>
+  </si>
+  <si>
+    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
+  </si>
+  <si>
+    <t>Profile screen loads fields for user settings adjustments</t>
+  </si>
+  <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-APP-24</t>
+  </si>
+  <si>
+    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
+  </si>
+  <si>
+    <t>Display Name changes update the user info values on Save</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-APP-25</t>
+  </si>
+  <si>
+    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
+  </si>
+  <si>
+    <t>Preferred currency symbol alters default currency label layout</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-APP-26</t>
+  </si>
+  <si>
+    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
+  </si>
+  <si>
+    <t>Dialog queries permissions access to camera device for receipts scan</t>
+  </si>
+  <si>
+    <t>TC-APP-27</t>
+  </si>
+  <si>
+    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
+  </si>
+  <si>
+    <t>Toggling dark theme alters app styling variables colors</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-APP-28</t>
+  </si>
+  <si>
+    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
+  </si>
+  <si>
+    <t>Logout prompts verification warning dialog</t>
   </si>
   <si>
     <t>0.12s</t>
   </si>
   <si>
-    <t>TC-APP-03</t>
-  </si>
-  <si>
-    <t>TC-APP-03: Validate login email address format checking rules</t>
-  </si>
-  <si>
-    <t>Error label displays when email format is invalid</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-APP-04</t>
-  </si>
-  <si>
-    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
-  </si>
-  <si>
-    <t>App registers biometric device setup option in local state</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-APP-05</t>
-  </si>
-  <si>
-    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
-  </si>
-  <si>
-    <t>Dashboard balance, income, and expense summary widgets render</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-APP-06</t>
-  </si>
-  <si>
-    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
-  </si>
-  <si>
-    <t>Balance summary card resolves within view limits</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-APP-07</t>
-  </si>
-  <si>
-    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
-  </si>
-  <si>
-    <t>Pull to refresh updates transaction listings from background storage</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-APP-08</t>
-  </si>
-  <si>
-    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
-  </si>
-  <si>
-    <t>Income sheet modal slides into view</t>
-  </si>
-  <si>
-    <t>TC-APP-09</t>
-  </si>
-  <si>
-    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
-  </si>
-  <si>
-    <t>Category select holds Salary, Freelance, and Investments options</t>
-  </si>
-  <si>
-    <t>TC-APP-10</t>
-  </si>
-  <si>
-    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
-  </si>
-  <si>
-    <t>Income fields accept numeric and descriptive inputs</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-APP-11</t>
-  </si>
-  <si>
-    <t>TC-APP-11: Validate empty income form submission error indicators</t>
-  </si>
-  <si>
-    <t>Missing amount triggers mobile error highlights</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-APP-12</t>
-  </si>
-  <si>
-    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
-  </si>
-  <si>
-    <t>Expense sheet slides up with focus on Category dropdown</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-APP-13</t>
-  </si>
-  <si>
-    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
-  </si>
-  <si>
-    <t>Expense logging works and decreases overall dashboard balance</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-APP-14</t>
-  </si>
-  <si>
-    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
-  </si>
-  <si>
-    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
-  </si>
-  <si>
-    <t>TC-APP-15</t>
-  </si>
-  <si>
-    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
-  </si>
-  <si>
-    <t>Soft keyboard changes to numeric layout on amount field focus</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-APP-16</t>
-  </si>
-  <si>
-    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
-  </si>
-  <si>
-    <t>Active budget progress limiters are visible</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-APP-17</t>
-  </si>
-  <si>
-    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
-  </si>
-  <si>
-    <t>Progress bar limits adjust to new budget configurations</t>
-  </si>
-  <si>
-    <t>TC-APP-18</t>
-  </si>
-  <si>
-    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
-  </si>
-  <si>
-    <t>Alert popup loads when transaction breaches designated cap threshold</t>
-  </si>
-  <si>
-    <t>TC-APP-19</t>
-  </si>
-  <si>
-    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
-  </si>
-  <si>
-    <t>Distribution chart switches between absolute values and percentages</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-APP-20</t>
-  </si>
-  <si>
-    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
-  </si>
-  <si>
-    <t>Push alert fires sending current limits allocations reminders</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-APP-21</t>
-  </si>
-  <si>
-    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
-  </si>
-  <si>
-    <t>Successful transactions prompt immediate mobile success toast alert</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-APP-22</t>
-  </si>
-  <si>
-    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
-  </si>
-  <si>
-    <t>Swiping a notification alert row removes it from notifications panel</t>
-  </si>
-  <si>
-    <t>TC-APP-23</t>
-  </si>
-  <si>
-    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
-  </si>
-  <si>
-    <t>Profile screen loads fields for user settings adjustments</t>
-  </si>
-  <si>
-    <t>TC-APP-24</t>
-  </si>
-  <si>
-    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
-  </si>
-  <si>
-    <t>Display Name changes update the user info values on Save</t>
-  </si>
-  <si>
-    <t>TC-APP-25</t>
-  </si>
-  <si>
-    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
-  </si>
-  <si>
-    <t>Preferred currency symbol alters default currency label layout</t>
-  </si>
-  <si>
-    <t>TC-APP-26</t>
-  </si>
-  <si>
-    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
-  </si>
-  <si>
-    <t>Dialog queries permissions access to camera device for receipts scan</t>
-  </si>
-  <si>
-    <t>TC-APP-27</t>
-  </si>
-  <si>
-    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
-  </si>
-  <si>
-    <t>Toggling dark theme alters app styling variables colors</t>
-  </si>
-  <si>
-    <t>TC-APP-28</t>
-  </si>
-  <si>
-    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
-  </si>
-  <si>
-    <t>Logout prompts verification warning dialog</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
     <t>TC-APP-29</t>
   </si>
   <si>
@@ -406,9 +418,6 @@
     <t>Double tap exits execution thread and backgrounds app</t>
   </si>
   <si>
-    <t>0.19s</t>
-  </si>
-  <si>
     <t>TC-APP-30</t>
   </si>
   <si>
@@ -416,9 +425,6 @@
   </si>
   <si>
     <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
-  </si>
-  <si>
-    <t>0.29s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1381,21 +1387,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1404,21 +1410,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1427,21 +1433,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1450,21 +1456,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1473,7 +1479,7 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1496,21 +1502,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1519,7 +1525,7 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1588,21 +1594,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1611,21 +1617,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1634,21 +1640,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1657,7 +1663,7 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1680,21 +1686,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1703,7 +1709,7 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1726,21 +1732,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1749,21 +1755,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1772,21 +1778,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1795,21 +1801,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1818,21 +1824,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1841,21 +1847,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1864,21 +1870,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1887,7 +1893,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1919,27 +1925,27 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1962,19 +1968,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1982,16 +1988,16 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1999,16 +2005,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2016,16 +2022,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2050,16 +2056,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2067,16 +2073,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2084,16 +2090,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2101,16 +2107,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2118,16 +2124,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2152,16 +2158,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2169,16 +2175,16 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2186,16 +2192,16 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2203,16 +2209,16 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2254,16 +2260,16 @@
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2271,16 +2277,16 @@
         <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2288,16 +2294,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2339,16 +2345,16 @@
         <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2373,16 +2379,16 @@
         <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2410,7 +2416,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2424,16 +2430,16 @@
         <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2441,16 +2447,16 @@
         <v>3</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2458,16 +2464,16 @@
         <v>3</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2475,16 +2481,16 @@
         <v>3</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2492,16 +2498,16 @@
         <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2509,16 +2515,16 @@
         <v>3</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2529,7 +2535,7 @@
         <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
@@ -2546,7 +2552,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
@@ -2560,16 +2566,16 @@
         <v>3</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2580,7 +2586,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -2594,16 +2600,16 @@
         <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2611,16 +2617,16 @@
         <v>3</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2628,16 +2634,16 @@
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2645,16 +2651,16 @@
         <v>3</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2662,16 +2668,16 @@
         <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2679,16 +2685,16 @@
         <v>3</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2716,7 +2722,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
@@ -2747,16 +2753,16 @@
         <v>3</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2781,16 +2787,16 @@
         <v>3</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2798,16 +2804,16 @@
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2815,16 +2821,16 @@
         <v>3</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2832,16 +2838,16 @@
         <v>3</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2849,16 +2855,16 @@
         <v>3</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2883,16 +2889,16 @@
         <v>3</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2900,16 +2906,16 @@
         <v>3</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2917,16 +2923,16 @@
         <v>3</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2934,16 +2940,16 @@
         <v>3</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2951,16 +2957,16 @@
         <v>3</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2968,16 +2974,16 @@
         <v>3</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2985,16 +2991,16 @@
         <v>3</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3002,16 +3008,16 @@
         <v>3</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3019,16 +3025,16 @@
         <v>3</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3036,16 +3042,16 @@
         <v>3</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3056,7 +3062,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
@@ -3073,7 +3079,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
@@ -3090,7 +3096,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
@@ -3124,7 +3130,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
@@ -3138,16 +3144,16 @@
         <v>3</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3172,16 +3178,16 @@
         <v>3</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3189,16 +3195,16 @@
         <v>3</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3206,16 +3212,16 @@
         <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3223,16 +3229,16 @@
         <v>3</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3240,16 +3246,16 @@
         <v>3</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3260,7 +3266,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3274,16 +3280,16 @@
         <v>3</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3291,16 +3297,16 @@
         <v>3</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3308,16 +3314,16 @@
         <v>3</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3325,16 +3331,16 @@
         <v>3</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3345,7 +3351,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3362,7 +3368,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3379,7 +3385,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
@@ -3396,7 +3402,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
@@ -3413,7 +3419,7 @@
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
@@ -3427,16 +3433,16 @@
         <v>3</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3447,7 +3453,7 @@
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="206">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/18/2026, 5:58:09 AM</t>
+    <t>6/18/2026, 4:42:18 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>9.54s</t>
+    <t>8.43s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.35s</t>
+    <t>0.26s</t>
   </si>
   <si>
     <t>TC-APP-02</t>
@@ -115,316 +115,310 @@
     <t>App prevents submission on empty email or password fields</t>
   </si>
   <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-APP-03</t>
+  </si>
+  <si>
+    <t>TC-APP-03: Validate login email address format checking rules</t>
+  </si>
+  <si>
+    <t>Error label displays when email format is invalid</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-APP-04</t>
+  </si>
+  <si>
+    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
+  </si>
+  <si>
+    <t>App registers biometric device setup option in local state</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-APP-05</t>
+  </si>
+  <si>
+    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
+  </si>
+  <si>
+    <t>Dashboard balance, income, and expense summary widgets render</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-APP-06</t>
+  </si>
+  <si>
+    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
+  </si>
+  <si>
+    <t>Balance summary card resolves within view limits</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-APP-07</t>
+  </si>
+  <si>
+    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
+  </si>
+  <si>
+    <t>Pull to refresh updates transaction listings from background storage</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-APP-08</t>
+  </si>
+  <si>
+    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
+  </si>
+  <si>
+    <t>Income sheet modal slides into view</t>
+  </si>
+  <si>
+    <t>TC-APP-09</t>
+  </si>
+  <si>
+    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
+  </si>
+  <si>
+    <t>Category select holds Salary, Freelance, and Investments options</t>
+  </si>
+  <si>
+    <t>TC-APP-10</t>
+  </si>
+  <si>
+    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
+  </si>
+  <si>
+    <t>Income fields accept numeric and descriptive inputs</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-APP-11</t>
+  </si>
+  <si>
+    <t>TC-APP-11: Validate empty income form submission error indicators</t>
+  </si>
+  <si>
+    <t>Missing amount triggers mobile error highlights</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-APP-12</t>
+  </si>
+  <si>
+    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
+  </si>
+  <si>
+    <t>Expense sheet slides up with focus on Category dropdown</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-APP-13</t>
+  </si>
+  <si>
+    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
+  </si>
+  <si>
+    <t>Expense logging works and decreases overall dashboard balance</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-APP-14</t>
+  </si>
+  <si>
+    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
+  </si>
+  <si>
+    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
+  </si>
+  <si>
+    <t>TC-APP-15</t>
+  </si>
+  <si>
+    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
+  </si>
+  <si>
+    <t>Soft keyboard changes to numeric layout on amount field focus</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-APP-16</t>
+  </si>
+  <si>
+    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
+  </si>
+  <si>
+    <t>Active budget progress limiters are visible</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-APP-17</t>
+  </si>
+  <si>
+    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
+  </si>
+  <si>
+    <t>Progress bar limits adjust to new budget configurations</t>
+  </si>
+  <si>
+    <t>TC-APP-18</t>
+  </si>
+  <si>
+    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
+  </si>
+  <si>
+    <t>Alert popup loads when transaction breaches designated cap threshold</t>
+  </si>
+  <si>
+    <t>TC-APP-19</t>
+  </si>
+  <si>
+    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
+  </si>
+  <si>
+    <t>Distribution chart switches between absolute values and percentages</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-APP-20</t>
+  </si>
+  <si>
+    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
+  </si>
+  <si>
+    <t>Push alert fires sending current limits allocations reminders</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-APP-21</t>
+  </si>
+  <si>
+    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
+  </si>
+  <si>
+    <t>Successful transactions prompt immediate mobile success toast alert</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-APP-22</t>
+  </si>
+  <si>
+    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
+  </si>
+  <si>
+    <t>Swiping a notification alert row removes it from notifications panel</t>
+  </si>
+  <si>
+    <t>TC-APP-23</t>
+  </si>
+  <si>
+    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
+  </si>
+  <si>
+    <t>Profile screen loads fields for user settings adjustments</t>
+  </si>
+  <si>
+    <t>TC-APP-24</t>
+  </si>
+  <si>
+    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
+  </si>
+  <si>
+    <t>Display Name changes update the user info values on Save</t>
+  </si>
+  <si>
+    <t>TC-APP-25</t>
+  </si>
+  <si>
+    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
+  </si>
+  <si>
+    <t>Preferred currency symbol alters default currency label layout</t>
+  </si>
+  <si>
+    <t>TC-APP-26</t>
+  </si>
+  <si>
+    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
+  </si>
+  <si>
+    <t>Dialog queries permissions access to camera device for receipts scan</t>
+  </si>
+  <si>
+    <t>TC-APP-27</t>
+  </si>
+  <si>
+    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
+  </si>
+  <si>
+    <t>Toggling dark theme alters app styling variables colors</t>
+  </si>
+  <si>
+    <t>TC-APP-28</t>
+  </si>
+  <si>
+    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
+  </si>
+  <si>
+    <t>Logout prompts verification warning dialog</t>
+  </si>
+  <si>
     <t>0.40s</t>
   </si>
   <si>
-    <t>TC-APP-03</t>
-  </si>
-  <si>
-    <t>TC-APP-03: Validate login email address format checking rules</t>
-  </si>
-  <si>
-    <t>Error label displays when email format is invalid</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-APP-04</t>
-  </si>
-  <si>
-    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
-  </si>
-  <si>
-    <t>App registers biometric device setup option in local state</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-APP-05</t>
-  </si>
-  <si>
-    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
-  </si>
-  <si>
-    <t>Dashboard balance, income, and expense summary widgets render</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-APP-06</t>
-  </si>
-  <si>
-    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
-  </si>
-  <si>
-    <t>Balance summary card resolves within view limits</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-APP-07</t>
-  </si>
-  <si>
-    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
-  </si>
-  <si>
-    <t>Pull to refresh updates transaction listings from background storage</t>
+    <t>TC-APP-29</t>
+  </si>
+  <si>
+    <t>TC-APP-29: Verify double tap mobile back button exits the application safely</t>
+  </si>
+  <si>
+    <t>Double tap exits execution thread and backgrounds app</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-APP-30</t>
+  </si>
+  <si>
+    <t>TC-APP-30: Verify complete authentication details and cached tokens wipe on Logout</t>
+  </si>
+  <si>
+    <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
   </si>
   <si>
     <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-APP-08</t>
-  </si>
-  <si>
-    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
-  </si>
-  <si>
-    <t>Income sheet modal slides into view</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-APP-09</t>
-  </si>
-  <si>
-    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
-  </si>
-  <si>
-    <t>Category select holds Salary, Freelance, and Investments options</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-APP-10</t>
-  </si>
-  <si>
-    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
-  </si>
-  <si>
-    <t>Income fields accept numeric and descriptive inputs</t>
-  </si>
-  <si>
-    <t>TC-APP-11</t>
-  </si>
-  <si>
-    <t>TC-APP-11: Validate empty income form submission error indicators</t>
-  </si>
-  <si>
-    <t>Missing amount triggers mobile error highlights</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-APP-12</t>
-  </si>
-  <si>
-    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
-  </si>
-  <si>
-    <t>Expense sheet slides up with focus on Category dropdown</t>
-  </si>
-  <si>
-    <t>TC-APP-13</t>
-  </si>
-  <si>
-    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
-  </si>
-  <si>
-    <t>Expense logging works and decreases overall dashboard balance</t>
-  </si>
-  <si>
-    <t>TC-APP-14</t>
-  </si>
-  <si>
-    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
-  </si>
-  <si>
-    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-APP-15</t>
-  </si>
-  <si>
-    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
-  </si>
-  <si>
-    <t>Soft keyboard changes to numeric layout on amount field focus</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-APP-16</t>
-  </si>
-  <si>
-    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
-  </si>
-  <si>
-    <t>Active budget progress limiters are visible</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-APP-17</t>
-  </si>
-  <si>
-    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
-  </si>
-  <si>
-    <t>Progress bar limits adjust to new budget configurations</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-APP-18</t>
-  </si>
-  <si>
-    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
-  </si>
-  <si>
-    <t>Alert popup loads when transaction breaches designated cap threshold</t>
-  </si>
-  <si>
-    <t>TC-APP-19</t>
-  </si>
-  <si>
-    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
-  </si>
-  <si>
-    <t>Distribution chart switches between absolute values and percentages</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-APP-20</t>
-  </si>
-  <si>
-    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
-  </si>
-  <si>
-    <t>Push alert fires sending current limits allocations reminders</t>
-  </si>
-  <si>
-    <t>TC-APP-21</t>
-  </si>
-  <si>
-    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
-  </si>
-  <si>
-    <t>Successful transactions prompt immediate mobile success toast alert</t>
-  </si>
-  <si>
-    <t>TC-APP-22</t>
-  </si>
-  <si>
-    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
-  </si>
-  <si>
-    <t>Swiping a notification alert row removes it from notifications panel</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-APP-23</t>
-  </si>
-  <si>
-    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
-  </si>
-  <si>
-    <t>Profile screen loads fields for user settings adjustments</t>
-  </si>
-  <si>
-    <t>0.47s</t>
-  </si>
-  <si>
-    <t>TC-APP-24</t>
-  </si>
-  <si>
-    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
-  </si>
-  <si>
-    <t>Display Name changes update the user info values on Save</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-APP-25</t>
-  </si>
-  <si>
-    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
-  </si>
-  <si>
-    <t>Preferred currency symbol alters default currency label layout</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-APP-26</t>
-  </si>
-  <si>
-    <t>TC-APP-26: Verify app permissions prompt request triggers for Camera hardware access</t>
-  </si>
-  <si>
-    <t>Dialog queries permissions access to camera device for receipts scan</t>
-  </si>
-  <si>
-    <t>TC-APP-27</t>
-  </si>
-  <si>
-    <t>TC-APP-27: Verify system dark theme toggling switch interactions</t>
-  </si>
-  <si>
-    <t>Toggling dark theme alters app styling variables colors</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-APP-28</t>
-  </si>
-  <si>
-    <t>TC-APP-28: Verify opening mobile logout confirmation alert dialog panel</t>
-  </si>
-  <si>
-    <t>Logout prompts verification warning dialog</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-APP-29</t>
-  </si>
-  <si>
-    <t>TC-APP-29: Verify double tap mobile back button exits the application safely</t>
-  </si>
-  <si>
-    <t>Double tap exits execution thread and backgrounds app</t>
-  </si>
-  <si>
-    <t>TC-APP-30</t>
-  </si>
-  <si>
-    <t>TC-APP-30: Verify complete authentication details and cached tokens wipe on Logout</t>
-  </si>
-  <si>
-    <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1387,21 +1381,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1410,21 +1404,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1433,21 +1427,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1456,21 +1450,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1479,7 +1473,7 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1502,21 +1496,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1525,7 +1519,7 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1594,21 +1588,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1617,21 +1611,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1640,21 +1634,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1663,7 +1657,7 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1686,21 +1680,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1709,7 +1703,7 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1732,21 +1726,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1755,21 +1749,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1778,21 +1772,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1801,21 +1795,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1824,21 +1818,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1847,21 +1841,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1870,21 +1864,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1893,7 +1887,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>61</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1925,27 +1919,27 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1968,19 +1962,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1988,16 +1982,16 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2005,16 +1999,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2022,16 +2016,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2056,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2073,16 +2067,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2090,16 +2084,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2107,16 +2101,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2124,16 +2118,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2158,16 +2152,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2175,16 +2169,16 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2192,16 +2186,16 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2209,16 +2203,16 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2260,16 +2254,16 @@
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2277,16 +2271,16 @@
         <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2294,16 +2288,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2345,16 +2339,16 @@
         <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2379,16 +2373,16 @@
         <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2416,7 +2410,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2430,16 +2424,16 @@
         <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2447,16 +2441,16 @@
         <v>3</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2464,16 +2458,16 @@
         <v>3</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2481,16 +2475,16 @@
         <v>3</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2498,16 +2492,16 @@
         <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2515,16 +2509,16 @@
         <v>3</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2535,7 +2529,7 @@
         <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
@@ -2552,7 +2546,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
@@ -2566,16 +2560,16 @@
         <v>3</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2586,7 +2580,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -2600,16 +2594,16 @@
         <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2617,16 +2611,16 @@
         <v>3</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2634,16 +2628,16 @@
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2651,16 +2645,16 @@
         <v>3</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2668,16 +2662,16 @@
         <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2685,16 +2679,16 @@
         <v>3</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2722,7 +2716,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
@@ -2753,16 +2747,16 @@
         <v>3</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2787,16 +2781,16 @@
         <v>3</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2804,16 +2798,16 @@
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2821,16 +2815,16 @@
         <v>3</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2838,16 +2832,16 @@
         <v>3</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2855,16 +2849,16 @@
         <v>3</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2889,16 +2883,16 @@
         <v>3</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2906,16 +2900,16 @@
         <v>3</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2923,16 +2917,16 @@
         <v>3</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2940,16 +2934,16 @@
         <v>3</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2957,16 +2951,16 @@
         <v>3</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2974,16 +2968,16 @@
         <v>3</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2991,16 +2985,16 @@
         <v>3</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3008,16 +3002,16 @@
         <v>3</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3025,16 +3019,16 @@
         <v>3</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3042,16 +3036,16 @@
         <v>3</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3062,7 +3056,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
@@ -3079,7 +3073,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
@@ -3096,7 +3090,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
@@ -3130,7 +3124,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
@@ -3144,16 +3138,16 @@
         <v>3</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3178,16 +3172,16 @@
         <v>3</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3195,16 +3189,16 @@
         <v>3</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3212,16 +3206,16 @@
         <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3229,16 +3223,16 @@
         <v>3</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3246,16 +3240,16 @@
         <v>3</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3266,7 +3260,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3280,16 +3274,16 @@
         <v>3</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3297,16 +3291,16 @@
         <v>3</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3314,16 +3308,16 @@
         <v>3</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3331,16 +3325,16 @@
         <v>3</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3351,7 +3345,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3368,7 +3362,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3385,7 +3379,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
@@ -3402,7 +3396,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
@@ -3419,7 +3413,7 @@
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
@@ -3433,16 +3427,16 @@
         <v>3</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3453,7 +3447,7 @@
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="207">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/18/2026, 4:42:18 AM</t>
+    <t>6/18/2026, 6:11:46 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.43s</t>
+    <t>9.09s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,270 +103,279 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-APP-02</t>
+  </si>
+  <si>
+    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
+  </si>
+  <si>
+    <t>App prevents submission on empty email or password fields</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-APP-03</t>
+  </si>
+  <si>
+    <t>TC-APP-03: Validate login email address format checking rules</t>
+  </si>
+  <si>
+    <t>Error label displays when email format is invalid</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-APP-04</t>
+  </si>
+  <si>
+    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
+  </si>
+  <si>
+    <t>App registers biometric device setup option in local state</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-APP-05</t>
+  </si>
+  <si>
+    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
+  </si>
+  <si>
+    <t>Dashboard balance, income, and expense summary widgets render</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-APP-06</t>
+  </si>
+  <si>
+    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
+  </si>
+  <si>
+    <t>Balance summary card resolves within view limits</t>
+  </si>
+  <si>
+    <t>TC-APP-07</t>
+  </si>
+  <si>
+    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
+  </si>
+  <si>
+    <t>Pull to refresh updates transaction listings from background storage</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-APP-08</t>
+  </si>
+  <si>
+    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
+  </si>
+  <si>
+    <t>Income sheet modal slides into view</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-APP-09</t>
+  </si>
+  <si>
+    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
+  </si>
+  <si>
+    <t>Category select holds Salary, Freelance, and Investments options</t>
+  </si>
+  <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-APP-10</t>
+  </si>
+  <si>
+    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
+  </si>
+  <si>
+    <t>Income fields accept numeric and descriptive inputs</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-APP-11</t>
+  </si>
+  <si>
+    <t>TC-APP-11: Validate empty income form submission error indicators</t>
+  </si>
+  <si>
+    <t>Missing amount triggers mobile error highlights</t>
+  </si>
+  <si>
+    <t>TC-APP-12</t>
+  </si>
+  <si>
+    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
+  </si>
+  <si>
+    <t>Expense sheet slides up with focus on Category dropdown</t>
+  </si>
+  <si>
     <t>0.26s</t>
   </si>
   <si>
-    <t>TC-APP-02</t>
-  </si>
-  <si>
-    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
-  </si>
-  <si>
-    <t>App prevents submission on empty email or password fields</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-APP-03</t>
-  </si>
-  <si>
-    <t>TC-APP-03: Validate login email address format checking rules</t>
-  </si>
-  <si>
-    <t>Error label displays when email format is invalid</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-APP-04</t>
-  </si>
-  <si>
-    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
-  </si>
-  <si>
-    <t>App registers biometric device setup option in local state</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-APP-05</t>
-  </si>
-  <si>
-    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
-  </si>
-  <si>
-    <t>Dashboard balance, income, and expense summary widgets render</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-APP-06</t>
-  </si>
-  <si>
-    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
-  </si>
-  <si>
-    <t>Balance summary card resolves within view limits</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-APP-07</t>
-  </si>
-  <si>
-    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
-  </si>
-  <si>
-    <t>Pull to refresh updates transaction listings from background storage</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-APP-08</t>
-  </si>
-  <si>
-    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
-  </si>
-  <si>
-    <t>Income sheet modal slides into view</t>
-  </si>
-  <si>
-    <t>TC-APP-09</t>
-  </si>
-  <si>
-    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
-  </si>
-  <si>
-    <t>Category select holds Salary, Freelance, and Investments options</t>
-  </si>
-  <si>
-    <t>TC-APP-10</t>
-  </si>
-  <si>
-    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
-  </si>
-  <si>
-    <t>Income fields accept numeric and descriptive inputs</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-APP-11</t>
-  </si>
-  <si>
-    <t>TC-APP-11: Validate empty income form submission error indicators</t>
-  </si>
-  <si>
-    <t>Missing amount triggers mobile error highlights</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-APP-12</t>
-  </si>
-  <si>
-    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
-  </si>
-  <si>
-    <t>Expense sheet slides up with focus on Category dropdown</t>
+    <t>TC-APP-13</t>
+  </si>
+  <si>
+    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
+  </si>
+  <si>
+    <t>Expense logging works and decreases overall dashboard balance</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-APP-14</t>
+  </si>
+  <si>
+    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
+  </si>
+  <si>
+    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-APP-15</t>
+  </si>
+  <si>
+    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
+  </si>
+  <si>
+    <t>Soft keyboard changes to numeric layout on amount field focus</t>
+  </si>
+  <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-APP-16</t>
+  </si>
+  <si>
+    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
+  </si>
+  <si>
+    <t>Active budget progress limiters are visible</t>
+  </si>
+  <si>
+    <t>TC-APP-17</t>
+  </si>
+  <si>
+    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
+  </si>
+  <si>
+    <t>Progress bar limits adjust to new budget configurations</t>
+  </si>
+  <si>
+    <t>TC-APP-18</t>
+  </si>
+  <si>
+    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
+  </si>
+  <si>
+    <t>Alert popup loads when transaction breaches designated cap threshold</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-APP-19</t>
+  </si>
+  <si>
+    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
+  </si>
+  <si>
+    <t>Distribution chart switches between absolute values and percentages</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-APP-20</t>
+  </si>
+  <si>
+    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
+  </si>
+  <si>
+    <t>Push alert fires sending current limits allocations reminders</t>
+  </si>
+  <si>
+    <t>TC-APP-21</t>
+  </si>
+  <si>
+    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
+  </si>
+  <si>
+    <t>Successful transactions prompt immediate mobile success toast alert</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-APP-22</t>
+  </si>
+  <si>
+    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
+  </si>
+  <si>
+    <t>Swiping a notification alert row removes it from notifications panel</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-APP-23</t>
+  </si>
+  <si>
+    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
+  </si>
+  <si>
+    <t>Profile screen loads fields for user settings adjustments</t>
+  </si>
+  <si>
+    <t>TC-APP-24</t>
+  </si>
+  <si>
+    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
+  </si>
+  <si>
+    <t>Display Name changes update the user info values on Save</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-APP-25</t>
+  </si>
+  <si>
+    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
+  </si>
+  <si>
+    <t>Preferred currency symbol alters default currency label layout</t>
   </si>
   <si>
     <t>0.14s</t>
   </si>
   <si>
-    <t>TC-APP-13</t>
-  </si>
-  <si>
-    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
-  </si>
-  <si>
-    <t>Expense logging works and decreases overall dashboard balance</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-APP-14</t>
-  </si>
-  <si>
-    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
-  </si>
-  <si>
-    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
-  </si>
-  <si>
-    <t>TC-APP-15</t>
-  </si>
-  <si>
-    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
-  </si>
-  <si>
-    <t>Soft keyboard changes to numeric layout on amount field focus</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-APP-16</t>
-  </si>
-  <si>
-    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
-  </si>
-  <si>
-    <t>Active budget progress limiters are visible</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-APP-17</t>
-  </si>
-  <si>
-    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
-  </si>
-  <si>
-    <t>Progress bar limits adjust to new budget configurations</t>
-  </si>
-  <si>
-    <t>TC-APP-18</t>
-  </si>
-  <si>
-    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
-  </si>
-  <si>
-    <t>Alert popup loads when transaction breaches designated cap threshold</t>
-  </si>
-  <si>
-    <t>TC-APP-19</t>
-  </si>
-  <si>
-    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
-  </si>
-  <si>
-    <t>Distribution chart switches between absolute values and percentages</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-APP-20</t>
-  </si>
-  <si>
-    <t>TC-APP-20: Verify daily category budget limits reminder push alert system</t>
-  </si>
-  <si>
-    <t>Push alert fires sending current limits allocations reminders</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-APP-21</t>
-  </si>
-  <si>
-    <t>TC-APP-21: Verify transaction logged success notification alert feedback</t>
-  </si>
-  <si>
-    <t>Successful transactions prompt immediate mobile success toast alert</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-APP-22</t>
-  </si>
-  <si>
-    <t>TC-APP-22: Verify notification list swipe actions clearance</t>
-  </si>
-  <si>
-    <t>Swiping a notification alert row removes it from notifications panel</t>
-  </si>
-  <si>
-    <t>TC-APP-23</t>
-  </si>
-  <si>
-    <t>TC-APP-23: Verify navigating to user Profile settings tab</t>
-  </si>
-  <si>
-    <t>Profile screen loads fields for user settings adjustments</t>
-  </si>
-  <si>
-    <t>TC-APP-24</t>
-  </si>
-  <si>
-    <t>TC-APP-24: Verify editing display name metadata field updates sync</t>
-  </si>
-  <si>
-    <t>Display Name changes update the user info values on Save</t>
-  </si>
-  <si>
-    <t>TC-APP-25</t>
-  </si>
-  <si>
-    <t>TC-APP-25: Verify changing preferred default currency symbol updates settings</t>
-  </si>
-  <si>
-    <t>Preferred currency symbol alters default currency label layout</t>
-  </si>
-  <si>
     <t>TC-APP-26</t>
   </si>
   <si>
@@ -376,6 +385,9 @@
     <t>Dialog queries permissions access to camera device for receipts scan</t>
   </si>
   <si>
+    <t>0.38s</t>
+  </si>
+  <si>
     <t>TC-APP-27</t>
   </si>
   <si>
@@ -394,9 +406,6 @@
     <t>Logout prompts verification warning dialog</t>
   </si>
   <si>
-    <t>0.40s</t>
-  </si>
-  <si>
     <t>TC-APP-29</t>
   </si>
   <si>
@@ -406,9 +415,6 @@
     <t>Double tap exits execution thread and backgrounds app</t>
   </si>
   <si>
-    <t>0.19s</t>
-  </si>
-  <si>
     <t>TC-APP-30</t>
   </si>
   <si>
@@ -416,9 +422,6 @@
   </si>
   <si>
     <t>Logout deletes auth tokens and cleans cached shared preference namespaces</t>
-  </si>
-  <si>
-    <t>0.29s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1335,21 +1338,21 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1358,21 +1361,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1381,7 +1384,7 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1404,21 +1407,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1427,21 +1430,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1450,7 +1453,7 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1519,21 +1522,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1542,21 +1545,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1565,7 +1568,7 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1588,7 +1591,7 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1611,21 +1614,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1634,21 +1637,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1657,7 +1660,7 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1703,21 +1706,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1726,21 +1729,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1749,21 +1752,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1772,21 +1775,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1795,21 +1798,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>29</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1818,21 +1821,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1841,21 +1844,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1864,21 +1867,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>130</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1887,7 +1890,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1919,27 +1922,27 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1962,19 +1965,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1982,16 +1985,16 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1999,16 +2002,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2016,16 +2019,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2050,16 +2053,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2067,16 +2070,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2084,16 +2087,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2101,16 +2104,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2118,16 +2121,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2152,16 +2155,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2169,16 +2172,16 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2186,16 +2189,16 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2203,16 +2206,16 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2254,16 +2257,16 @@
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2271,16 +2274,16 @@
         <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2288,16 +2291,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2339,16 +2342,16 @@
         <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2359,7 +2362,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2373,16 +2376,16 @@
         <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2393,7 +2396,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2424,16 +2427,16 @@
         <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2441,16 +2444,16 @@
         <v>3</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2458,16 +2461,16 @@
         <v>3</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2475,16 +2478,16 @@
         <v>3</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2492,16 +2495,16 @@
         <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2509,16 +2512,16 @@
         <v>3</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2529,7 +2532,7 @@
         <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
@@ -2546,7 +2549,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
@@ -2560,16 +2563,16 @@
         <v>3</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2594,16 +2597,16 @@
         <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2611,16 +2614,16 @@
         <v>3</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2628,16 +2631,16 @@
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2645,16 +2648,16 @@
         <v>3</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2662,16 +2665,16 @@
         <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2679,16 +2682,16 @@
         <v>3</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2733,7 +2736,7 @@
         <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
@@ -2747,16 +2750,16 @@
         <v>3</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2767,7 +2770,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
@@ -2781,16 +2784,16 @@
         <v>3</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2798,16 +2801,16 @@
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2815,16 +2818,16 @@
         <v>3</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2832,16 +2835,16 @@
         <v>3</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2849,16 +2852,16 @@
         <v>3</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2883,16 +2886,16 @@
         <v>3</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2900,16 +2903,16 @@
         <v>3</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2917,16 +2920,16 @@
         <v>3</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2934,16 +2937,16 @@
         <v>3</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2951,16 +2954,16 @@
         <v>3</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2968,16 +2971,16 @@
         <v>3</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2985,16 +2988,16 @@
         <v>3</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3002,16 +3005,16 @@
         <v>3</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3019,16 +3022,16 @@
         <v>3</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3036,16 +3039,16 @@
         <v>3</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3073,7 +3076,7 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
@@ -3090,7 +3093,7 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
@@ -3138,16 +3141,16 @@
         <v>3</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3158,7 +3161,7 @@
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3172,16 +3175,16 @@
         <v>3</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3189,16 +3192,16 @@
         <v>3</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3206,16 +3209,16 @@
         <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3223,16 +3226,16 @@
         <v>3</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3240,16 +3243,16 @@
         <v>3</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3260,7 +3263,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3274,16 +3277,16 @@
         <v>3</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3291,16 +3294,16 @@
         <v>3</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3308,16 +3311,16 @@
         <v>3</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3325,16 +3328,16 @@
         <v>3</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3345,7 +3348,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3362,7 +3365,7 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3379,7 +3382,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
@@ -3396,7 +3399,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
@@ -3413,7 +3416,7 @@
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
@@ -3427,16 +3430,16 @@
         <v>3</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3447,7 +3450,7 @@
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -24,7 +24,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>18/6/2026, 12:06:19 pm</t>
+    <t>18/6/2026, 12:08:55 pm</t>
   </si>
   <si>
     <t>Test Suite / Scope</t>
@@ -96,1566 +96,1578 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-APP-002</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-APP-003</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-APP-004</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-APP-005</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-APP-006</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-APP-007</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-APP-008</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-APP-009</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-APP-010</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>0.49s</t>
+  </si>
+  <si>
+    <t>TC-APP-011</t>
+  </si>
+  <si>
+    <t>Registration Screen</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-APP-012</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-013</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-APP-014</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-APP-015</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-APP-016</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-APP-017</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-APP-018</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-019</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-APP-020</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-APP-021</t>
+  </si>
+  <si>
+    <t>Forgot Password Screen</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-APP-022</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-APP-023</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-024</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-APP-025</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-APP-026</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-027</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-APP-028</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-APP-029</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-030</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-031</t>
+  </si>
+  <si>
+    <t>OTP Verification Screen</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-032</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-033</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-034</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-035</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-036</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-APP-037</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-038</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-APP-039</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-040</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-041</t>
+  </si>
+  <si>
+    <t>Multi-Factor Auth Screen</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-042</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-043</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-044</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-045</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-APP-046</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-047</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-048</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.50s</t>
+  </si>
+  <si>
+    <t>TC-APP-049</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-050</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>0.11s</t>
+  </si>
+  <si>
+    <t>TC-APP-051</t>
+  </si>
+  <si>
+    <t>Host Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-052</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-053</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-APP-054</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-055</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 5 without validation errors</t>
+  </si>
+  <si>
     <t>0.21s</t>
   </si>
   <si>
-    <t>TC-APP-002</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-APP-003</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 3 without validation errors</t>
+    <t>TC-APP-056</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-057</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-058</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-059</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-060</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-061</t>
+  </si>
+  <si>
+    <t>Guard Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 1 without validation errors</t>
   </si>
   <si>
     <t>0.44s</t>
   </si>
   <si>
-    <t>TC-APP-004</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-005</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-APP-006</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-APP-007</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 7 without validation errors</t>
+    <t>TC-APP-062</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-063</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-064</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.10s</t>
+  </si>
+  <si>
+    <t>TC-APP-065</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-066</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-APP-067</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-068</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-APP-069</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-070</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-071</t>
+  </si>
+  <si>
+    <t>Admin Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-072</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-073</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-074</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-075</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-076</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-077</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-078</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-APP-079</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-080</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-081</t>
+  </si>
+  <si>
+    <t>Visitor Logs Screen</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-082</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-083</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-084</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-085</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-086</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-087</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-088</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-APP-089</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-090</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-091</t>
+  </si>
+  <si>
+    <t>Scan QR Screen</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-092</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-093</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-094</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-095</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-096</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-097</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-098</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-099</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-100</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-101</t>
+  </si>
+  <si>
+    <t>Face Verify Screen</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-102</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-103</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-104</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-105</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-106</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-107</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-108</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-109</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-110</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-APP-111</t>
+  </si>
+  <si>
+    <t>Profile Screen</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-112</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-113</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-114</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-115</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-116</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-117</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-118</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-119</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-120</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-121</t>
+  </si>
+  <si>
+    <t>Settings Screen</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-122</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-123</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-124</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-125</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-126</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-127</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-128</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-129</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-130</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-131</t>
+  </si>
+  <si>
+    <t>Pass Preview Screen</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-132</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-133</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-134</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-135</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-136</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-137</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-138</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-139</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-APP-140</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-141</t>
+  </si>
+  <si>
+    <t>Active Visitor Details Screen</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-142</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-143</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-144</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-145</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-146</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-147</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-148</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-149</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-150</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-151</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details Screen</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-152</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-153</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-154</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-155</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-APP-156</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-APP-157</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 7 without validation errors</t>
   </si>
   <si>
     <t>0.48s</t>
   </si>
   <si>
-    <t>TC-APP-008</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-009</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-010</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-APP-011</t>
-  </si>
-  <si>
-    <t>Registration Screen</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-APP-012</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-APP-013</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.10s</t>
-  </si>
-  <si>
-    <t>TC-APP-014</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-APP-015</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.19s</t>
-  </si>
-  <si>
-    <t>TC-APP-016</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-017</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-APP-018</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.11s</t>
-  </si>
-  <si>
-    <t>TC-APP-019</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-020</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-APP-021</t>
-  </si>
-  <si>
-    <t>Forgot Password Screen</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.50s</t>
-  </si>
-  <si>
-    <t>TC-APP-022</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-023</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-024</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-025</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-APP-026</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-027</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-APP-028</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-029</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-030</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-APP-031</t>
-  </si>
-  <si>
-    <t>OTP Verification Screen</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-APP-032</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
-    <t>TC-APP-033</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-APP-034</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-035</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-APP-036</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-APP-037</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-038</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-039</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-040</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-041</t>
-  </si>
-  <si>
-    <t>Multi-Factor Auth Screen</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-042</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-APP-043</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-APP-044</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-APP-045</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-046</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-APP-047</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-048</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-049</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-APP-050</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.47s</t>
-  </si>
-  <si>
-    <t>TC-APP-051</t>
-  </si>
-  <si>
-    <t>Host Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-052</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-APP-053</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-054</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-055</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-056</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-APP-057</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-058</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-APP-059</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-060</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-061</t>
-  </si>
-  <si>
-    <t>Guard Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-062</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-063</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-064</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-065</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-066</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-067</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-068</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-069</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-070</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-071</t>
-  </si>
-  <si>
-    <t>Admin Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-072</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-073</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-074</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-075</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-076</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-077</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-078</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-079</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-080</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-081</t>
-  </si>
-  <si>
-    <t>Visitor Logs Screen</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-082</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-083</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-084</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-085</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-086</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-087</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-088</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-089</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-090</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-091</t>
-  </si>
-  <si>
-    <t>Scan QR Screen</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-092</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-093</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-094</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-095</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-096</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-097</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-098</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-099</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-100</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-101</t>
-  </si>
-  <si>
-    <t>Face Verify Screen</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-102</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-103</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-104</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-105</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-106</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-107</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-108</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-109</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-110</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-111</t>
-  </si>
-  <si>
-    <t>Profile Screen</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-112</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-113</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-114</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-115</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-116</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-APP-117</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-118</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-119</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-120</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-121</t>
-  </si>
-  <si>
-    <t>Settings Screen</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-122</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-123</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-124</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-APP-125</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-126</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-127</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-128</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-129</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-130</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-131</t>
-  </si>
-  <si>
-    <t>Pass Preview Screen</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-132</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-APP-133</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-134</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-135</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-136</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-137</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-138</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-139</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-140</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-141</t>
-  </si>
-  <si>
-    <t>Active Visitor Details Screen</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-APP-142</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-143</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-144</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-145</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-146</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-147</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-148</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-149</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-150</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-151</t>
-  </si>
-  <si>
-    <t>Upcoming Visit Details Screen</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-152</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-153</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-154</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-155</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-156</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-APP-157</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 7 without validation errors</t>
-  </si>
-  <si>
     <t>TC-APP-158</t>
   </si>
   <si>
@@ -1704,9 +1716,6 @@
     <t>System should complete Generate Pass Screen action 2 without validation errors</t>
   </si>
   <si>
-    <t>0.32s</t>
-  </si>
-  <si>
     <t>TC-APP-163</t>
   </si>
   <si>
@@ -1947,9 +1956,6 @@
     <t>System should complete Theme Settings Screen action 8 without validation errors</t>
   </si>
   <si>
-    <t>0.49s</t>
-  </si>
-  <si>
     <t>TC-APP-189</t>
   </si>
   <si>
@@ -2061,9 +2067,6 @@
     <t>System should complete Currency Settings Screen action 10 without validation errors</t>
   </si>
   <si>
-    <t>0.45s</t>
-  </si>
-  <si>
     <t>TC-APP-201</t>
   </si>
   <si>
@@ -2146,9 +2149,6 @@
   </si>
   <si>
     <t>System should complete Language Settings Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.28s</t>
   </si>
   <si>
     <t>TC-APP-210</t>
@@ -3652,21 +3652,21 @@
         <v>26</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
@@ -3675,21 +3675,21 @@
         <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>25</v>
@@ -3698,21 +3698,21 @@
         <v>26</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -3721,21 +3721,21 @@
         <v>26</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
@@ -3744,21 +3744,21 @@
         <v>26</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -3767,21 +3767,21 @@
         <v>26</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
@@ -3790,21 +3790,21 @@
         <v>26</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
@@ -3813,21 +3813,21 @@
         <v>26</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
@@ -3836,21 +3836,21 @@
         <v>26</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
@@ -3859,21 +3859,21 @@
         <v>26</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
@@ -3882,21 +3882,21 @@
         <v>26</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
@@ -3905,21 +3905,21 @@
         <v>26</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
@@ -3928,21 +3928,21 @@
         <v>26</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -3951,21 +3951,21 @@
         <v>26</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
@@ -3974,21 +3974,21 @@
         <v>26</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -3997,21 +3997,21 @@
         <v>26</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -4020,21 +4020,21 @@
         <v>26</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -4043,21 +4043,21 @@
         <v>26</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -4066,21 +4066,21 @@
         <v>26</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
@@ -4089,21 +4089,21 @@
         <v>26</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -4112,21 +4112,21 @@
         <v>26</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -4135,21 +4135,21 @@
         <v>26</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>25</v>
@@ -4158,21 +4158,21 @@
         <v>26</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>25</v>
@@ -4181,21 +4181,21 @@
         <v>26</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>25</v>
@@ -4204,44 +4204,44 @@
         <v>26</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>25</v>
@@ -4250,21 +4250,21 @@
         <v>26</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>25</v>
@@ -4273,21 +4273,21 @@
         <v>26</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>25</v>
@@ -4296,21 +4296,21 @@
         <v>26</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>143</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>25</v>
@@ -4319,21 +4319,21 @@
         <v>26</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>25</v>
@@ -4342,21 +4342,21 @@
         <v>26</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>25</v>
@@ -4365,21 +4365,21 @@
         <v>26</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>25</v>
@@ -4388,21 +4388,21 @@
         <v>26</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>25</v>
@@ -4411,21 +4411,21 @@
         <v>26</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>25</v>
@@ -4434,21 +4434,21 @@
         <v>26</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>25</v>
@@ -4457,21 +4457,21 @@
         <v>26</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>25</v>
@@ -4480,21 +4480,21 @@
         <v>26</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>25</v>
@@ -4503,21 +4503,21 @@
         <v>26</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>25</v>
@@ -4526,21 +4526,21 @@
         <v>26</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>25</v>
@@ -4549,7 +4549,7 @@
         <v>26</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -4557,7 +4557,7 @@
         <v>183</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>184</v>
@@ -4572,30 +4572,30 @@
         <v>26</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -4603,7 +4603,7 @@
         <v>190</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>191</v>
@@ -4618,22 +4618,22 @@
         <v>26</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>193</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="E48" s="3" t="s">
         <v>25</v>
       </c>
@@ -4641,30 +4641,30 @@
         <v>26</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -4672,7 +4672,7 @@
         <v>200</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>201</v>
@@ -4687,45 +4687,45 @@
         <v>26</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>203</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="E52" s="3" t="s">
         <v>25</v>
       </c>
@@ -4733,22 +4733,22 @@
         <v>26</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="E53" s="3" t="s">
         <v>25</v>
       </c>
@@ -4756,45 +4756,45 @@
         <v>26</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>215</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="E54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="E55" s="3" t="s">
         <v>25</v>
       </c>
@@ -4802,30 +4802,30 @@
         <v>26</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C56" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="E56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4833,7 +4833,7 @@
         <v>225</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>226</v>
@@ -4848,22 +4848,22 @@
         <v>26</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="E58" s="3" t="s">
         <v>25</v>
       </c>
@@ -4871,22 +4871,22 @@
         <v>26</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="E59" s="3" t="s">
         <v>25</v>
       </c>
@@ -4894,22 +4894,22 @@
         <v>26</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>235</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="E60" s="3" t="s">
         <v>25</v>
       </c>
@@ -4917,22 +4917,22 @@
         <v>26</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>203</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="E61" s="3" t="s">
         <v>25</v>
       </c>
@@ -4940,45 +4940,45 @@
         <v>26</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="D62" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="E62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="E63" s="3" t="s">
         <v>25</v>
       </c>
@@ -4986,22 +4986,22 @@
         <v>26</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>228</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C64" s="3" t="s">
+      <c r="D64" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>251</v>
-      </c>
       <c r="E64" s="3" t="s">
         <v>25</v>
       </c>
@@ -5009,30 +5009,30 @@
         <v>26</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>42</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C65" s="3" t="s">
+      <c r="D65" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="E65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -5040,7 +5040,7 @@
         <v>255</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>256</v>
@@ -5055,7 +5055,7 @@
         <v>26</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>42</v>
+        <v>199</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -5063,7 +5063,7 @@
         <v>258</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>259</v>
@@ -5078,21 +5078,21 @@
         <v>26</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>27</v>
+        <v>261</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>25</v>
@@ -5101,21 +5101,21 @@
         <v>26</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>88</v>
+        <v>254</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>25</v>
@@ -5124,21 +5124,21 @@
         <v>26</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>186</v>
+        <v>268</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>25</v>
@@ -5147,21 +5147,21 @@
         <v>26</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>60</v>
+        <v>199</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>25</v>
@@ -5170,21 +5170,21 @@
         <v>26</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>143</v>
+        <v>254</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>25</v>
@@ -5193,21 +5193,21 @@
         <v>26</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>25</v>
@@ -5216,21 +5216,21 @@
         <v>26</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>25</v>
@@ -5239,21 +5239,21 @@
         <v>26</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>25</v>
@@ -5262,21 +5262,21 @@
         <v>26</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>25</v>
@@ -5285,21 +5285,21 @@
         <v>26</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>25</v>
@@ -5308,21 +5308,21 @@
         <v>26</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>25</v>
@@ -5331,21 +5331,21 @@
         <v>26</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>25</v>
@@ -5354,21 +5354,21 @@
         <v>26</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>207</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>25</v>
@@ -5377,21 +5377,21 @@
         <v>26</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>178</v>
+        <v>254</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>25</v>
@@ -5400,21 +5400,21 @@
         <v>26</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>228</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>25</v>
@@ -5423,21 +5423,21 @@
         <v>26</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="C83" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>25</v>
@@ -5446,21 +5446,21 @@
         <v>26</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>193</v>
+        <v>98</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>25</v>
@@ -5469,21 +5469,21 @@
         <v>26</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>25</v>
@@ -5492,21 +5492,21 @@
         <v>26</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>203</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>25</v>
@@ -5515,21 +5515,21 @@
         <v>26</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>25</v>
@@ -5538,21 +5538,21 @@
         <v>26</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>25</v>
@@ -5561,21 +5561,21 @@
         <v>26</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>25</v>
@@ -5584,21 +5584,21 @@
         <v>26</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>207</v>
+        <v>332</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>25</v>
@@ -5607,21 +5607,21 @@
         <v>26</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>25</v>
@@ -5630,21 +5630,21 @@
         <v>26</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>193</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>25</v>
@@ -5653,21 +5653,21 @@
         <v>26</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>25</v>
@@ -5676,21 +5676,21 @@
         <v>26</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>25</v>
@@ -5699,21 +5699,21 @@
         <v>26</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>25</v>
@@ -5722,21 +5722,21 @@
         <v>26</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>25</v>
@@ -5745,21 +5745,21 @@
         <v>26</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>31</v>
+        <v>268</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>25</v>
@@ -5768,21 +5768,21 @@
         <v>26</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>31</v>
+        <v>268</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>25</v>
@@ -5791,21 +5791,21 @@
         <v>26</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>31</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>25</v>
@@ -5814,21 +5814,21 @@
         <v>26</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>25</v>
@@ -5837,21 +5837,21 @@
         <v>26</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>25</v>
@@ -5860,21 +5860,21 @@
         <v>26</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>25</v>
@@ -5883,21 +5883,21 @@
         <v>26</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>25</v>
@@ -5906,21 +5906,21 @@
         <v>26</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>25</v>
@@ -5929,21 +5929,21 @@
         <v>26</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>25</v>
@@ -5952,21 +5952,21 @@
         <v>26</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>178</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>25</v>
@@ -5975,21 +5975,21 @@
         <v>26</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>25</v>
@@ -5998,21 +5998,21 @@
         <v>26</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>25</v>
@@ -6021,21 +6021,21 @@
         <v>26</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>31</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>25</v>
@@ -6044,21 +6044,21 @@
         <v>26</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>228</v>
+        <v>51</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>25</v>
@@ -6067,21 +6067,21 @@
         <v>26</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>25</v>
@@ -6090,21 +6090,21 @@
         <v>26</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>158</v>
+        <v>401</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>25</v>
@@ -6113,21 +6113,21 @@
         <v>26</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>69</v>
+        <v>332</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>25</v>
@@ -6136,21 +6136,21 @@
         <v>26</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>178</v>
+        <v>224</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>25</v>
@@ -6159,21 +6159,21 @@
         <v>26</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>25</v>
@@ -6182,21 +6182,21 @@
         <v>26</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>25</v>
@@ -6205,21 +6205,21 @@
         <v>26</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>35</v>
+        <v>300</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>25</v>
@@ -6228,21 +6228,21 @@
         <v>26</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>416</v>
+        <v>75</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>25</v>
@@ -6251,21 +6251,21 @@
         <v>26</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>25</v>
@@ -6274,21 +6274,21 @@
         <v>26</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>203</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>25</v>
@@ -6297,21 +6297,21 @@
         <v>26</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>25</v>
@@ -6320,21 +6320,21 @@
         <v>26</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>215</v>
+        <v>75</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>25</v>
@@ -6343,21 +6343,21 @@
         <v>26</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>215</v>
+        <v>35</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>25</v>
@@ -6366,21 +6366,21 @@
         <v>26</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>25</v>
@@ -6389,21 +6389,21 @@
         <v>26</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>25</v>
@@ -6412,21 +6412,21 @@
         <v>26</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>442</v>
+        <v>27</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>25</v>
@@ -6435,21 +6435,21 @@
         <v>26</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>25</v>
@@ -6458,21 +6458,21 @@
         <v>26</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>186</v>
+        <v>79</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>25</v>
@@ -6481,21 +6481,21 @@
         <v>26</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>25</v>
@@ -6504,21 +6504,21 @@
         <v>26</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>143</v>
+        <v>244</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>25</v>
@@ -6527,21 +6527,21 @@
         <v>26</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>25</v>
@@ -6550,21 +6550,21 @@
         <v>26</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>25</v>
@@ -6573,21 +6573,21 @@
         <v>26</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>235</v>
+        <v>59</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B133" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>462</v>
-      </c>
       <c r="C133" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>25</v>
@@ -6596,21 +6596,21 @@
         <v>26</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>468</v>
+        <v>68</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>25</v>
@@ -6619,21 +6619,21 @@
         <v>26</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>154</v>
+        <v>300</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>25</v>
@@ -6642,21 +6642,21 @@
         <v>26</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>25</v>
@@ -6665,21 +6665,21 @@
         <v>26</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>25</v>
@@ -6688,21 +6688,21 @@
         <v>26</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>25</v>
@@ -6711,21 +6711,21 @@
         <v>26</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>416</v>
+        <v>55</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>25</v>
@@ -6734,21 +6734,21 @@
         <v>26</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>207</v>
+        <v>43</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>25</v>
@@ -6757,21 +6757,21 @@
         <v>26</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>65</v>
+        <v>492</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>25</v>
@@ -6780,21 +6780,21 @@
         <v>26</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>25</v>
@@ -6803,21 +6803,21 @@
         <v>26</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>497</v>
+        <v>118</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>25</v>
@@ -6826,21 +6826,21 @@
         <v>26</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>25</v>
@@ -6849,21 +6849,21 @@
         <v>26</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>186</v>
+        <v>107</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>25</v>
@@ -6872,21 +6872,21 @@
         <v>26</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>25</v>
@@ -6895,21 +6895,21 @@
         <v>26</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>25</v>
@@ -6918,21 +6918,21 @@
         <v>26</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>215</v>
+        <v>79</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>25</v>
@@ -6941,21 +6941,21 @@
         <v>26</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>124</v>
+        <v>332</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>25</v>
@@ -6964,21 +6964,21 @@
         <v>26</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>25</v>
@@ -6987,21 +6987,21 @@
         <v>26</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>228</v>
+        <v>133</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>25</v>
@@ -7010,21 +7010,21 @@
         <v>26</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>25</v>
@@ -7033,21 +7033,21 @@
         <v>26</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>178</v>
+        <v>59</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>25</v>
@@ -7056,21 +7056,21 @@
         <v>26</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>25</v>
@@ -7079,21 +7079,21 @@
         <v>26</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>134</v>
+        <v>332</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>25</v>
@@ -7102,21 +7102,21 @@
         <v>26</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>25</v>
@@ -7125,21 +7125,21 @@
         <v>26</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>92</v>
+        <v>543</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>25</v>
@@ -7148,21 +7148,21 @@
         <v>26</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>25</v>
@@ -7171,21 +7171,21 @@
         <v>26</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>186</v>
+        <v>550</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>25</v>
@@ -7194,21 +7194,21 @@
         <v>26</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>25</v>
@@ -7217,21 +7217,21 @@
         <v>26</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>228</v>
+        <v>118</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>25</v>
@@ -7240,21 +7240,21 @@
         <v>26</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>25</v>
@@ -7263,21 +7263,21 @@
         <v>26</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>215</v>
+        <v>166</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>25</v>
@@ -7286,21 +7286,21 @@
         <v>26</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>563</v>
+        <v>91</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>25</v>
@@ -7309,21 +7309,21 @@
         <v>26</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>25</v>
@@ -7332,21 +7332,21 @@
         <v>26</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>25</v>
@@ -7355,21 +7355,21 @@
         <v>26</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>25</v>
@@ -7378,21 +7378,21 @@
         <v>26</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>178</v>
+        <v>43</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>25</v>
@@ -7401,21 +7401,21 @@
         <v>26</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>203</v>
+        <v>332</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>25</v>
@@ -7424,21 +7424,21 @@
         <v>26</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>25</v>
@@ -7447,21 +7447,21 @@
         <v>26</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>25</v>
@@ -7470,21 +7470,21 @@
         <v>26</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>228</v>
+        <v>133</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>25</v>
@@ -7493,21 +7493,21 @@
         <v>26</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>46</v>
+        <v>224</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="B173" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="B173" s="3" t="s">
-        <v>589</v>
-      </c>
       <c r="C173" s="3" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>25</v>
@@ -7516,21 +7516,21 @@
         <v>26</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>25</v>
@@ -7539,21 +7539,21 @@
         <v>26</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>25</v>
@@ -7562,21 +7562,21 @@
         <v>26</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>442</v>
+        <v>59</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>25</v>
@@ -7585,21 +7585,21 @@
         <v>26</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>178</v>
+        <v>543</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>25</v>
@@ -7608,21 +7608,21 @@
         <v>26</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>25</v>
@@ -7631,21 +7631,21 @@
         <v>26</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>25</v>
@@ -7654,21 +7654,21 @@
         <v>26</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>203</v>
+        <v>122</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>25</v>
@@ -7677,21 +7677,21 @@
         <v>26</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>563</v>
+        <v>107</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>25</v>
@@ -7700,21 +7700,21 @@
         <v>26</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>134</v>
+        <v>543</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>25</v>
@@ -7723,21 +7723,21 @@
         <v>26</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B183" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="B183" s="3" t="s">
-        <v>620</v>
-      </c>
       <c r="C183" s="3" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>25</v>
@@ -7746,21 +7746,21 @@
         <v>26</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>497</v>
+        <v>55</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>25</v>
@@ -7769,21 +7769,21 @@
         <v>26</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>92</v>
+        <v>332</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>25</v>
@@ -7792,21 +7792,21 @@
         <v>26</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>143</v>
+        <v>39</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>25</v>
@@ -7815,21 +7815,21 @@
         <v>26</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>25</v>
@@ -7838,21 +7838,21 @@
         <v>26</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>563</v>
+        <v>75</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>25</v>
@@ -7861,21 +7861,21 @@
         <v>26</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>497</v>
+        <v>98</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>25</v>
@@ -7884,21 +7884,21 @@
         <v>26</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>644</v>
+        <v>79</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>25</v>
@@ -7907,21 +7907,21 @@
         <v>26</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>644</v>
+        <v>51</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>25</v>
@@ -7930,21 +7930,21 @@
         <v>26</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>25</v>
@@ -7953,21 +7953,21 @@
         <v>26</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>25</v>
@@ -7976,21 +7976,21 @@
         <v>26</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>25</v>
@@ -7999,21 +7999,21 @@
         <v>26</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>46</v>
+        <v>159</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>25</v>
@@ -8022,21 +8022,21 @@
         <v>26</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>50</v>
+        <v>199</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>25</v>
@@ -8045,21 +8045,21 @@
         <v>26</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>563</v>
+        <v>35</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>25</v>
@@ -8068,21 +8068,21 @@
         <v>26</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>178</v>
+        <v>401</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>25</v>
@@ -8091,21 +8091,21 @@
         <v>26</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>25</v>
@@ -8114,21 +8114,21 @@
         <v>26</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>25</v>
@@ -8137,21 +8137,21 @@
         <v>26</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>25</v>
@@ -8160,21 +8160,21 @@
         <v>26</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>682</v>
+        <v>47</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>25</v>
@@ -8183,21 +8183,21 @@
         <v>26</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>25</v>
@@ -8206,21 +8206,21 @@
         <v>26</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>25</v>
@@ -8229,21 +8229,21 @@
         <v>26</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>468</v>
+        <v>39</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>25</v>
@@ -8252,21 +8252,21 @@
         <v>26</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>228</v>
+        <v>31</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>25</v>
@@ -8275,21 +8275,21 @@
         <v>26</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>154</v>
+        <v>261</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>25</v>
@@ -8298,21 +8298,21 @@
         <v>26</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>25</v>
@@ -8321,21 +8321,21 @@
         <v>26</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>497</v>
+        <v>59</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>25</v>
@@ -8344,21 +8344,21 @@
         <v>26</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>31</v>
+        <v>261</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>25</v>
@@ -8367,7 +8367,7 @@
         <v>26</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>711</v>
+        <v>43</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -8375,7 +8375,7 @@
         <v>712</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>713</v>
@@ -8390,7 +8390,7 @@
         <v>26</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
         <v>26</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -8436,7 +8436,7 @@
         <v>26</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>682</v>
+        <v>261</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -8459,7 +8459,7 @@
         <v>26</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -8482,7 +8482,7 @@
         <v>26</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>65</v>
+        <v>189</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -8505,7 +8505,7 @@
         <v>26</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -8528,7 +8528,7 @@
         <v>26</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -8551,7 +8551,7 @@
         <v>26</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>193</v>
+        <v>543</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -8574,7 +8574,7 @@
         <v>26</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -8597,7 +8597,7 @@
         <v>26</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>682</v>
+        <v>122</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -8620,7 +8620,7 @@
         <v>26</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -8643,7 +8643,7 @@
         <v>26</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>203</v>
+        <v>129</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -8666,7 +8666,7 @@
         <v>26</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>178</v>
+        <v>102</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -8689,7 +8689,7 @@
         <v>26</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -8712,7 +8712,7 @@
         <v>26</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>182</v>
+        <v>63</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -8735,7 +8735,7 @@
         <v>26</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>682</v>
+        <v>300</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -8758,7 +8758,7 @@
         <v>26</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>178</v>
+        <v>401</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8781,7 +8781,7 @@
         <v>26</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>27</v>
+        <v>332</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8804,7 +8804,7 @@
         <v>26</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>228</v>
+        <v>55</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8827,7 +8827,7 @@
         <v>26</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8850,7 +8850,7 @@
         <v>26</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8873,7 +8873,7 @@
         <v>26</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>416</v>
+        <v>47</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8896,7 +8896,7 @@
         <v>26</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>31</v>
+        <v>332</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8919,7 +8919,7 @@
         <v>26</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>468</v>
+        <v>31</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8942,7 +8942,7 @@
         <v>26</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>644</v>
+        <v>254</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8965,7 +8965,7 @@
         <v>26</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8988,7 +8988,7 @@
         <v>26</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>215</v>
+        <v>43</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -9011,7 +9011,7 @@
         <v>26</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>644</v>
+        <v>122</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -9034,7 +9034,7 @@
         <v>26</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>154</v>
+        <v>300</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -9057,7 +9057,7 @@
         <v>26</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -9080,7 +9080,7 @@
         <v>26</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>235</v>
+        <v>166</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -9103,7 +9103,7 @@
         <v>26</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>193</v>
+        <v>83</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -9126,7 +9126,7 @@
         <v>26</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -9149,7 +9149,7 @@
         <v>26</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>215</v>
+        <v>129</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -9172,7 +9172,7 @@
         <v>26</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>139</v>
+        <v>401</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -9195,7 +9195,7 @@
         <v>26</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -9218,7 +9218,7 @@
         <v>26</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -9241,7 +9241,7 @@
         <v>26</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -9264,7 +9264,7 @@
         <v>26</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -9287,7 +9287,7 @@
         <v>26</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -9310,7 +9310,7 @@
         <v>26</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -9333,7 +9333,7 @@
         <v>26</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -9356,7 +9356,7 @@
         <v>26</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -9379,7 +9379,7 @@
         <v>26</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -9402,7 +9402,7 @@
         <v>26</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -9425,7 +9425,7 @@
         <v>26</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>65</v>
+        <v>332</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -9448,7 +9448,7 @@
         <v>26</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -9471,7 +9471,7 @@
         <v>26</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -9494,7 +9494,7 @@
         <v>26</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -9517,7 +9517,7 @@
         <v>26</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>182</v>
+        <v>43</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -9540,7 +9540,7 @@
         <v>26</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>228</v>
+        <v>39</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -9563,7 +9563,7 @@
         <v>26</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>235</v>
+        <v>543</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -9586,7 +9586,7 @@
         <v>26</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>143</v>
+        <v>189</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -9609,7 +9609,7 @@
         <v>26</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -9632,7 +9632,7 @@
         <v>26</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -9655,7 +9655,7 @@
         <v>26</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>65</v>
+        <v>492</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -9678,7 +9678,7 @@
         <v>26</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>215</v>
+        <v>129</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -9701,7 +9701,7 @@
         <v>26</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>215</v>
+        <v>83</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -9724,7 +9724,7 @@
         <v>26</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -9747,7 +9747,7 @@
         <v>26</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>147</v>
+        <v>401</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9770,7 +9770,7 @@
         <v>26</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9793,7 +9793,7 @@
         <v>26</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>42</v>
+        <v>244</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9816,7 +9816,7 @@
         <v>26</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9839,7 +9839,7 @@
         <v>26</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>193</v>
+        <v>543</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9862,7 +9862,7 @@
         <v>26</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9885,7 +9885,7 @@
         <v>26</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>644</v>
+        <v>102</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9908,7 +9908,7 @@
         <v>26</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>186</v>
+        <v>261</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9931,7 +9931,7 @@
         <v>26</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9954,7 +9954,7 @@
         <v>26</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9977,7 +9977,7 @@
         <v>26</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -10000,7 +10000,7 @@
         <v>26</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>442</v>
+        <v>206</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -10023,7 +10023,7 @@
         <v>26</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>31</v>
+        <v>300</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -10046,7 +10046,7 @@
         <v>26</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>235</v>
+        <v>51</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -10069,7 +10069,7 @@
         <v>26</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>563</v>
+        <v>47</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -10092,7 +10092,7 @@
         <v>26</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -10115,7 +10115,7 @@
         <v>26</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>497</v>
+        <v>268</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -10138,7 +10138,7 @@
         <v>26</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>203</v>
+        <v>129</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -10161,7 +10161,7 @@
         <v>26</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>42</v>
+        <v>550</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -10184,7 +10184,7 @@
         <v>26</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -10230,7 +10230,7 @@
         <v>26</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>203</v>
+        <v>83</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -10253,7 +10253,7 @@
         <v>26</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -10276,7 +10276,7 @@
         <v>26</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>228</v>
+        <v>550</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -10299,7 +10299,7 @@
         <v>26</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>88</v>
+        <v>261</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -10322,7 +10322,7 @@
         <v>26</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -10345,7 +10345,7 @@
         <v>26</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -10368,7 +10368,7 @@
         <v>26</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -10391,7 +10391,7 @@
         <v>26</v>
       </c>
       <c r="G298" s="3" t="s">
-        <v>134</v>
+        <v>268</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
         <v>26</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -10437,7 +10437,7 @@
         <v>26</v>
       </c>
       <c r="G300" s="3" t="s">
-        <v>99</v>
+        <v>268</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -10460,7 +10460,7 @@
         <v>26</v>
       </c>
       <c r="G301" s="3" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Appium_Report.xlsx
+++ b/reports/Appium_Report.xlsx
@@ -24,7 +24,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>18/6/2026, 12:29:47 pm</t>
+    <t>18/6/2026, 1:15:21 pm</t>
   </si>
   <si>
     <t>Test Suite / Scope</t>
